--- a/システム開発演習/030-試験/033-総合試験計画書兼結果書.xlsx
+++ b/システム開発演習/030-試験/033-総合試験計画書兼結果書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\030-試験\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDDD604-E9B8-465B-B77F-3B60896BE1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251DA48E-9438-43F0-ACAC-4E1EB4A943DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="67">
   <si>
     <t>システム名称</t>
     <rPh sb="4" eb="6">
@@ -583,6 +583,10 @@
     <t>パターン4</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -591,7 +595,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="明朝"/>
@@ -690,6 +694,12 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
       <family val="1"/>
       <charset val="128"/>
     </font>
@@ -1025,7 +1035,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1">
@@ -1077,26 +1087,66 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1125,33 +1175,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1164,40 +1187,34 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1590,206 +1607,205 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE22E59C-2FC1-464A-BC6F-6F5A1042534F}">
-  <dimension ref="A1:BQ129"/>
+  <dimension ref="A1:BO129"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="3.33203125" customWidth="1"/>
-    <col min="3" max="71" width="2.6640625" customWidth="1"/>
+    <col min="3" max="43" width="2.6640625" customWidth="1"/>
+    <col min="44" max="44" width="15.33203125" customWidth="1"/>
+    <col min="45" max="45" width="4.44140625" customWidth="1"/>
+    <col min="46" max="69" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="13.8" thickTop="1">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:49" ht="13.8" thickTop="1">
+      <c r="A1" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="51" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-      <c r="AE1" s="52"/>
-      <c r="AF1" s="52"/>
-      <c r="AG1" s="51" t="s">
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="53">
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="49">
         <v>45582</v>
       </c>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="54" t="s">
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="AU1" s="55"/>
-      <c r="AV1" s="36"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="38"/>
-    </row>
-    <row r="2" spans="1:51" ht="13.8" thickBot="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="42" t="s">
+      <c r="AT1" s="60"/>
+      <c r="AU1" s="50"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="52"/>
+    </row>
+    <row r="2" spans="1:49" ht="13.8" thickBot="1">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="43" t="s">
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="42" t="s">
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
-      <c r="AK2" s="44" t="s">
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="AL2" s="44"/>
-      <c r="AM2" s="44"/>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="44"/>
-      <c r="AP2" s="44"/>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="44"/>
-      <c r="AS2" s="44"/>
-      <c r="AT2" s="56"/>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="40"/>
-      <c r="AX2" s="41"/>
-    </row>
-    <row r="3" spans="1:51" ht="13.8" thickTop="1"/>
-    <row r="4" spans="1:51">
+      <c r="AL2" s="58"/>
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="58"/>
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="58"/>
+      <c r="AR2" s="58"/>
+      <c r="AS2" s="61"/>
+      <c r="AT2" s="62"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="54"/>
+      <c r="AW2" s="55"/>
+    </row>
+    <row r="3" spans="1:49" ht="13.8" thickTop="1"/>
+    <row r="4" spans="1:49">
       <c r="A4" s="6"/>
       <c r="B4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="31"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
       <c r="W4" s="9" t="s">
         <v>6</v>
       </c>
       <c r="X4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="Y4" s="29" t="s">
+      <c r="Y4" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="30"/>
-      <c r="AJ4" s="30"/>
-      <c r="AK4" s="30"/>
-      <c r="AL4" s="30"/>
-      <c r="AM4" s="30"/>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="30"/>
-      <c r="AQ4" s="31"/>
-      <c r="AR4" s="29" t="s">
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="64"/>
+      <c r="AE4" s="64"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="64"/>
+      <c r="AK4" s="64"/>
+      <c r="AL4" s="64"/>
+      <c r="AM4" s="64"/>
+      <c r="AN4" s="64"/>
+      <c r="AO4" s="64"/>
+      <c r="AP4" s="64"/>
+      <c r="AQ4" s="65"/>
+      <c r="AR4" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AS4" s="30"/>
-      <c r="AT4" s="30"/>
-      <c r="AU4" s="31"/>
-      <c r="AV4" s="29" t="s">
+      <c r="AS4" s="65"/>
+      <c r="AT4" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="AW4" s="30"/>
-      <c r="AX4" s="30"/>
-      <c r="AY4" s="31"/>
-    </row>
-    <row r="5" spans="1:51">
-      <c r="A5" s="32" t="s">
+      <c r="AU4" s="64"/>
+      <c r="AV4" s="64"/>
+      <c r="AW4" s="65"/>
+    </row>
+    <row r="5" spans="1:49" ht="18">
+      <c r="A5" s="66" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="8"/>
@@ -1835,17 +1851,19 @@
       <c r="AO5" s="5"/>
       <c r="AP5" s="5"/>
       <c r="AQ5" s="8"/>
-      <c r="AR5" s="7"/>
-      <c r="AS5" s="5"/>
-      <c r="AT5" s="5"/>
-      <c r="AU5" s="8"/>
-      <c r="AV5" s="7"/>
-      <c r="AW5" s="5"/>
-      <c r="AX5" s="5"/>
-      <c r="AY5" s="8"/>
-    </row>
-    <row r="6" spans="1:51">
-      <c r="A6" s="32"/>
+      <c r="AR5" s="71">
+        <v>45594</v>
+      </c>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="8"/>
+    </row>
+    <row r="6" spans="1:49">
+      <c r="A6" s="66"/>
       <c r="B6" s="8"/>
       <c r="C6" s="13" t="s">
         <v>29</v>
@@ -1892,16 +1910,14 @@
       <c r="AP6" s="5"/>
       <c r="AQ6" s="8"/>
       <c r="AR6" s="7"/>
-      <c r="AS6" s="5"/>
-      <c r="AT6" s="5"/>
-      <c r="AU6" s="8"/>
-      <c r="AV6" s="7"/>
-      <c r="AW6" s="5"/>
-      <c r="AX6" s="5"/>
-      <c r="AY6" s="8"/>
-    </row>
-    <row r="7" spans="1:51">
-      <c r="A7" s="32"/>
+      <c r="AS6" s="8"/>
+      <c r="AT6" s="7"/>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="5"/>
+      <c r="AW6" s="8"/>
+    </row>
+    <row r="7" spans="1:49">
+      <c r="A7" s="66"/>
       <c r="B7" s="8">
         <v>1</v>
       </c>
@@ -1949,17 +1965,15 @@
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
       <c r="AQ7" s="8"/>
-      <c r="AR7" s="7"/>
-      <c r="AS7" s="5"/>
-      <c r="AT7" s="5"/>
-      <c r="AU7" s="8"/>
-      <c r="AV7" s="7"/>
-      <c r="AW7" s="5"/>
-      <c r="AX7" s="5"/>
-      <c r="AY7" s="8"/>
-    </row>
-    <row r="8" spans="1:51">
-      <c r="A8" s="32"/>
+      <c r="AR7" s="70"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="7"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="8"/>
+    </row>
+    <row r="8" spans="1:49">
+      <c r="A8" s="66"/>
       <c r="B8" s="8">
         <v>2</v>
       </c>
@@ -2008,16 +2022,14 @@
       <c r="AP8" s="5"/>
       <c r="AQ8" s="8"/>
       <c r="AR8" s="7"/>
-      <c r="AS8" s="5"/>
-      <c r="AT8" s="5"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" s="7"/>
-      <c r="AW8" s="5"/>
-      <c r="AX8" s="5"/>
-      <c r="AY8" s="8"/>
-    </row>
-    <row r="9" spans="1:51">
-      <c r="A9" s="32"/>
+      <c r="AS8" s="8"/>
+      <c r="AT8" s="7"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="8"/>
+    </row>
+    <row r="9" spans="1:49">
+      <c r="A9" s="66"/>
       <c r="B9" s="8"/>
       <c r="C9" s="7"/>
       <c r="D9" s="5"/>
@@ -2060,16 +2072,14 @@
       <c r="AP9" s="5"/>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="7"/>
-      <c r="AS9" s="5"/>
-      <c r="AT9" s="5"/>
-      <c r="AU9" s="8"/>
-      <c r="AV9" s="7"/>
-      <c r="AW9" s="5"/>
-      <c r="AX9" s="5"/>
-      <c r="AY9" s="8"/>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" s="32"/>
+      <c r="AS9" s="8"/>
+      <c r="AT9" s="7"/>
+      <c r="AU9" s="5"/>
+      <c r="AV9" s="5"/>
+      <c r="AW9" s="8"/>
+    </row>
+    <row r="10" spans="1:49">
+      <c r="A10" s="66"/>
       <c r="B10" s="8"/>
       <c r="C10" s="7"/>
       <c r="D10" s="14" t="s">
@@ -2116,16 +2126,14 @@
       <c r="AP10" s="5"/>
       <c r="AQ10" s="8"/>
       <c r="AR10" s="7"/>
-      <c r="AS10" s="5"/>
-      <c r="AT10" s="5"/>
-      <c r="AU10" s="8"/>
-      <c r="AV10" s="7"/>
-      <c r="AW10" s="5"/>
-      <c r="AX10" s="5"/>
-      <c r="AY10" s="8"/>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" s="32"/>
+      <c r="AS10" s="8"/>
+      <c r="AT10" s="7"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="8"/>
+    </row>
+    <row r="11" spans="1:49">
+      <c r="A11" s="66"/>
       <c r="B11" s="8"/>
       <c r="C11" s="7"/>
       <c r="D11" s="5"/>
@@ -2170,16 +2178,14 @@
       <c r="AP11" s="5"/>
       <c r="AQ11" s="8"/>
       <c r="AR11" s="7"/>
-      <c r="AS11" s="5"/>
-      <c r="AT11" s="5"/>
-      <c r="AU11" s="8"/>
-      <c r="AV11" s="7"/>
-      <c r="AW11" s="5"/>
-      <c r="AX11" s="5"/>
-      <c r="AY11" s="8"/>
-    </row>
-    <row r="12" spans="1:51">
-      <c r="A12" s="32"/>
+      <c r="AS11" s="8"/>
+      <c r="AT11" s="7"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="8"/>
+    </row>
+    <row r="12" spans="1:49">
+      <c r="A12" s="66"/>
       <c r="B12" s="8"/>
       <c r="C12" s="7"/>
       <c r="D12" s="5"/>
@@ -2222,16 +2228,14 @@
       <c r="AP12" s="5"/>
       <c r="AQ12" s="8"/>
       <c r="AR12" s="7"/>
-      <c r="AS12" s="5"/>
-      <c r="AT12" s="5"/>
-      <c r="AU12" s="8"/>
-      <c r="AV12" s="7"/>
-      <c r="AW12" s="5"/>
-      <c r="AX12" s="5"/>
-      <c r="AY12" s="8"/>
-    </row>
-    <row r="13" spans="1:51">
-      <c r="A13" s="32"/>
+      <c r="AS12" s="8"/>
+      <c r="AT12" s="7"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="8"/>
+    </row>
+    <row r="13" spans="1:49">
+      <c r="A13" s="66"/>
       <c r="B13" s="8"/>
       <c r="C13" s="7"/>
       <c r="D13" s="5"/>
@@ -2276,16 +2280,14 @@
       <c r="AP13" s="5"/>
       <c r="AQ13" s="8"/>
       <c r="AR13" s="7"/>
-      <c r="AS13" s="5"/>
-      <c r="AT13" s="5"/>
-      <c r="AU13" s="8"/>
-      <c r="AV13" s="7"/>
-      <c r="AW13" s="5"/>
-      <c r="AX13" s="5"/>
-      <c r="AY13" s="8"/>
-    </row>
-    <row r="14" spans="1:51">
-      <c r="A14" s="32"/>
+      <c r="AS13" s="8"/>
+      <c r="AT13" s="7"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="8"/>
+    </row>
+    <row r="14" spans="1:49">
+      <c r="A14" s="66"/>
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="5"/>
@@ -2330,16 +2332,14 @@
       <c r="AP14" s="5"/>
       <c r="AQ14" s="8"/>
       <c r="AR14" s="7"/>
-      <c r="AS14" s="5"/>
-      <c r="AT14" s="5"/>
-      <c r="AU14" s="8"/>
-      <c r="AV14" s="7"/>
-      <c r="AW14" s="5"/>
-      <c r="AX14" s="5"/>
-      <c r="AY14" s="8"/>
-    </row>
-    <row r="15" spans="1:51">
-      <c r="A15" s="32"/>
+      <c r="AS14" s="8"/>
+      <c r="AT14" s="7"/>
+      <c r="AU14" s="5"/>
+      <c r="AV14" s="5"/>
+      <c r="AW14" s="8"/>
+    </row>
+    <row r="15" spans="1:49">
+      <c r="A15" s="66"/>
       <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="5"/>
@@ -2384,16 +2384,14 @@
       <c r="AP15" s="5"/>
       <c r="AQ15" s="8"/>
       <c r="AR15" s="7"/>
-      <c r="AS15" s="5"/>
-      <c r="AT15" s="5"/>
-      <c r="AU15" s="8"/>
-      <c r="AV15" s="7"/>
-      <c r="AW15" s="5"/>
-      <c r="AX15" s="5"/>
-      <c r="AY15" s="8"/>
-    </row>
-    <row r="16" spans="1:51">
-      <c r="A16" s="32"/>
+      <c r="AS15" s="8"/>
+      <c r="AT15" s="7"/>
+      <c r="AU15" s="5"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="8"/>
+    </row>
+    <row r="16" spans="1:49">
+      <c r="A16" s="66"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="5"/>
@@ -2438,16 +2436,14 @@
       <c r="AP16" s="5"/>
       <c r="AQ16" s="8"/>
       <c r="AR16" s="7"/>
-      <c r="AS16" s="5"/>
-      <c r="AT16" s="5"/>
-      <c r="AU16" s="8"/>
-      <c r="AV16" s="7"/>
-      <c r="AW16" s="5"/>
-      <c r="AX16" s="5"/>
-      <c r="AY16" s="8"/>
-    </row>
-    <row r="17" spans="1:54">
-      <c r="A17" s="32"/>
+      <c r="AS16" s="8"/>
+      <c r="AT16" s="7"/>
+      <c r="AU16" s="5"/>
+      <c r="AV16" s="5"/>
+      <c r="AW16" s="8"/>
+    </row>
+    <row r="17" spans="1:52">
+      <c r="A17" s="66"/>
       <c r="B17" s="8"/>
       <c r="C17" s="7"/>
       <c r="D17" s="5"/>
@@ -2492,16 +2488,14 @@
       <c r="AP17" s="5"/>
       <c r="AQ17" s="8"/>
       <c r="AR17" s="7"/>
-      <c r="AS17" s="5"/>
-      <c r="AT17" s="5"/>
-      <c r="AU17" s="8"/>
-      <c r="AV17" s="7"/>
-      <c r="AW17" s="5"/>
-      <c r="AX17" s="5"/>
-      <c r="AY17" s="8"/>
-    </row>
-    <row r="18" spans="1:54">
-      <c r="A18" s="32"/>
+      <c r="AS17" s="8"/>
+      <c r="AT17" s="7"/>
+      <c r="AU17" s="5"/>
+      <c r="AV17" s="5"/>
+      <c r="AW17" s="8"/>
+    </row>
+    <row r="18" spans="1:52">
+      <c r="A18" s="66"/>
       <c r="B18" s="8"/>
       <c r="C18" s="7"/>
       <c r="D18" s="5"/>
@@ -2544,16 +2538,14 @@
       <c r="AP18" s="5"/>
       <c r="AQ18" s="8"/>
       <c r="AR18" s="7"/>
-      <c r="AS18" s="5"/>
-      <c r="AT18" s="5"/>
-      <c r="AU18" s="8"/>
-      <c r="AV18" s="7"/>
-      <c r="AW18" s="5"/>
-      <c r="AX18" s="5"/>
-      <c r="AY18" s="8"/>
-    </row>
-    <row r="19" spans="1:54">
-      <c r="A19" s="32"/>
+      <c r="AS18" s="8"/>
+      <c r="AT18" s="7"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="8"/>
+    </row>
+    <row r="19" spans="1:52">
+      <c r="A19" s="66"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="5"/>
@@ -2598,16 +2590,14 @@
       <c r="AP19" s="5"/>
       <c r="AQ19" s="8"/>
       <c r="AR19" s="7"/>
-      <c r="AS19" s="5"/>
-      <c r="AT19" s="5"/>
-      <c r="AU19" s="8"/>
-      <c r="AV19" s="7"/>
-      <c r="AW19" s="5"/>
-      <c r="AX19" s="5"/>
-      <c r="AY19" s="8"/>
-    </row>
-    <row r="20" spans="1:54">
-      <c r="A20" s="32"/>
+      <c r="AS19" s="8"/>
+      <c r="AT19" s="7"/>
+      <c r="AU19" s="5"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="8"/>
+    </row>
+    <row r="20" spans="1:52">
+      <c r="A20" s="66"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="5"/>
@@ -2652,16 +2642,14 @@
       <c r="AP20" s="5"/>
       <c r="AQ20" s="8"/>
       <c r="AR20" s="7"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
-      <c r="AU20" s="8"/>
-      <c r="AV20" s="7"/>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="5"/>
-      <c r="AY20" s="8"/>
-    </row>
-    <row r="21" spans="1:54">
-      <c r="A21" s="32"/>
+      <c r="AS20" s="8"/>
+      <c r="AT20" s="7"/>
+      <c r="AU20" s="5"/>
+      <c r="AV20" s="5"/>
+      <c r="AW20" s="8"/>
+    </row>
+    <row r="21" spans="1:52">
+      <c r="A21" s="66"/>
       <c r="B21" s="8"/>
       <c r="C21" s="7"/>
       <c r="D21" s="5"/>
@@ -2706,16 +2694,14 @@
       <c r="AP21" s="5"/>
       <c r="AQ21" s="8"/>
       <c r="AR21" s="7"/>
-      <c r="AS21" s="5"/>
-      <c r="AT21" s="5"/>
-      <c r="AU21" s="8"/>
-      <c r="AV21" s="7"/>
-      <c r="AW21" s="5"/>
-      <c r="AX21" s="5"/>
-      <c r="AY21" s="8"/>
-    </row>
-    <row r="22" spans="1:54">
-      <c r="A22" s="32"/>
+      <c r="AS21" s="8"/>
+      <c r="AT21" s="7"/>
+      <c r="AU21" s="5"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="8"/>
+    </row>
+    <row r="22" spans="1:52">
+      <c r="A22" s="66"/>
       <c r="B22" s="8"/>
       <c r="C22" s="7"/>
       <c r="D22" s="5"/>
@@ -2760,16 +2746,14 @@
       <c r="AP22" s="5"/>
       <c r="AQ22" s="8"/>
       <c r="AR22" s="7"/>
-      <c r="AS22" s="5"/>
-      <c r="AT22" s="5"/>
-      <c r="AU22" s="8"/>
-      <c r="AV22" s="7"/>
-      <c r="AW22" s="5"/>
-      <c r="AX22" s="5"/>
-      <c r="AY22" s="8"/>
-    </row>
-    <row r="23" spans="1:54">
-      <c r="A23" s="32"/>
+      <c r="AS22" s="8"/>
+      <c r="AT22" s="7"/>
+      <c r="AU22" s="5"/>
+      <c r="AV22" s="5"/>
+      <c r="AW22" s="8"/>
+    </row>
+    <row r="23" spans="1:52">
+      <c r="A23" s="66"/>
       <c r="B23" s="8"/>
       <c r="C23" s="7"/>
       <c r="D23" s="5"/>
@@ -2814,16 +2798,14 @@
       <c r="AP23" s="5"/>
       <c r="AQ23" s="8"/>
       <c r="AR23" s="7"/>
-      <c r="AS23" s="5"/>
-      <c r="AT23" s="5"/>
-      <c r="AU23" s="8"/>
-      <c r="AV23" s="7"/>
-      <c r="AW23" s="5"/>
-      <c r="AX23" s="5"/>
-      <c r="AY23" s="8"/>
-    </row>
-    <row r="24" spans="1:54">
-      <c r="A24" s="32"/>
+      <c r="AS23" s="8"/>
+      <c r="AT23" s="7"/>
+      <c r="AU23" s="5"/>
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="8"/>
+    </row>
+    <row r="24" spans="1:52">
+      <c r="A24" s="66"/>
       <c r="B24" s="8"/>
       <c r="C24" s="7"/>
       <c r="D24" s="5"/>
@@ -2868,16 +2850,14 @@
       <c r="AP24" s="5"/>
       <c r="AQ24" s="8"/>
       <c r="AR24" s="7"/>
-      <c r="AS24" s="5"/>
-      <c r="AT24" s="5"/>
-      <c r="AU24" s="8"/>
-      <c r="AV24" s="7"/>
-      <c r="AW24" s="5"/>
-      <c r="AX24" s="5"/>
-      <c r="AY24" s="8"/>
-    </row>
-    <row r="25" spans="1:54">
-      <c r="A25" s="33"/>
+      <c r="AS24" s="8"/>
+      <c r="AT24" s="7"/>
+      <c r="AU24" s="5"/>
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="8"/>
+    </row>
+    <row r="25" spans="1:52">
+      <c r="A25" s="67"/>
       <c r="B25" s="12"/>
       <c r="C25" s="11"/>
       <c r="D25" s="10"/>
@@ -2921,19 +2901,17 @@
       <c r="AP25" s="10"/>
       <c r="AQ25" s="12"/>
       <c r="AR25" s="11"/>
-      <c r="AS25" s="10"/>
-      <c r="AT25" s="10"/>
-      <c r="AU25" s="12"/>
-      <c r="AV25" s="11"/>
-      <c r="AW25" s="10"/>
-      <c r="AX25" s="10"/>
-      <c r="AY25" s="12"/>
-      <c r="AZ25" s="7"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-    </row>
-    <row r="26" spans="1:54">
-      <c r="A26" s="34" t="s">
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="11"/>
+      <c r="AU25" s="10"/>
+      <c r="AV25" s="10"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="7"/>
+      <c r="AY25" s="5"/>
+      <c r="AZ25" s="5"/>
+    </row>
+    <row r="26" spans="1:52" ht="18">
+      <c r="A26" s="68" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="8"/>
@@ -2977,18 +2955,20 @@
       <c r="AO26" s="5"/>
       <c r="AP26" s="5"/>
       <c r="AQ26" s="8"/>
-      <c r="AR26" s="7"/>
-      <c r="AS26" s="5"/>
-      <c r="AT26" s="5"/>
-      <c r="AU26" s="8"/>
-      <c r="AV26" s="7"/>
-      <c r="AW26" s="5"/>
-      <c r="AX26" s="5"/>
-      <c r="AY26" s="8"/>
-      <c r="BA26" s="5"/>
-    </row>
-    <row r="27" spans="1:54">
-      <c r="A27" s="35"/>
+      <c r="AR26" s="71">
+        <v>45594</v>
+      </c>
+      <c r="AS26" s="8"/>
+      <c r="AT26" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU26" s="5"/>
+      <c r="AV26" s="5"/>
+      <c r="AW26" s="8"/>
+      <c r="AY26" s="5"/>
+    </row>
+    <row r="27" spans="1:52">
+      <c r="A27" s="69"/>
       <c r="B27" s="8"/>
       <c r="C27" s="13" t="s">
         <v>29</v>
@@ -3035,18 +3015,16 @@
       <c r="AP27" s="5"/>
       <c r="AQ27" s="8"/>
       <c r="AR27" s="7"/>
-      <c r="AS27" s="5"/>
-      <c r="AT27" s="5"/>
-      <c r="AU27" s="8"/>
-      <c r="AV27" s="7"/>
-      <c r="AW27" s="5"/>
-      <c r="AX27" s="5"/>
-      <c r="AY27" s="8"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="18"/>
-    </row>
-    <row r="28" spans="1:54">
-      <c r="A28" s="35"/>
+      <c r="AS27" s="8"/>
+      <c r="AT27" s="7"/>
+      <c r="AU27" s="5"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="8"/>
+      <c r="AY27" s="5"/>
+      <c r="AZ27" s="18"/>
+    </row>
+    <row r="28" spans="1:52">
+      <c r="A28" s="69"/>
       <c r="B28" s="8">
         <v>1</v>
       </c>
@@ -3095,18 +3073,16 @@
       <c r="AP28" s="5"/>
       <c r="AQ28" s="8"/>
       <c r="AR28" s="7"/>
-      <c r="AS28" s="5"/>
-      <c r="AT28" s="5"/>
-      <c r="AU28" s="8"/>
-      <c r="AV28" s="7"/>
-      <c r="AW28" s="5"/>
-      <c r="AX28" s="5"/>
-      <c r="AY28" s="8"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="18"/>
-    </row>
-    <row r="29" spans="1:54">
-      <c r="A29" s="35"/>
+      <c r="AS28" s="8"/>
+      <c r="AT28" s="7"/>
+      <c r="AU28" s="5"/>
+      <c r="AV28" s="5"/>
+      <c r="AW28" s="8"/>
+      <c r="AY28" s="5"/>
+      <c r="AZ28" s="18"/>
+    </row>
+    <row r="29" spans="1:52">
+      <c r="A29" s="69"/>
       <c r="B29" s="8">
         <v>2</v>
       </c>
@@ -3153,18 +3129,16 @@
       <c r="AP29" s="5"/>
       <c r="AQ29" s="8"/>
       <c r="AR29" s="7"/>
-      <c r="AS29" s="5"/>
-      <c r="AT29" s="5"/>
-      <c r="AU29" s="8"/>
-      <c r="AV29" s="7"/>
-      <c r="AW29" s="5"/>
-      <c r="AX29" s="5"/>
-      <c r="AY29" s="8"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="18"/>
-    </row>
-    <row r="30" spans="1:54">
-      <c r="A30" s="35"/>
+      <c r="AS29" s="8"/>
+      <c r="AT29" s="7"/>
+      <c r="AU29" s="5"/>
+      <c r="AV29" s="5"/>
+      <c r="AW29" s="8"/>
+      <c r="AY29" s="5"/>
+      <c r="AZ29" s="18"/>
+    </row>
+    <row r="30" spans="1:52">
+      <c r="A30" s="69"/>
       <c r="B30" s="8"/>
       <c r="C30" s="7"/>
       <c r="D30" s="5"/>
@@ -3209,18 +3183,16 @@
       <c r="AP30" s="5"/>
       <c r="AQ30" s="8"/>
       <c r="AR30" s="7"/>
-      <c r="AS30" s="5"/>
-      <c r="AT30" s="5"/>
-      <c r="AU30" s="8"/>
-      <c r="AV30" s="7"/>
-      <c r="AW30" s="5"/>
-      <c r="AX30" s="5"/>
-      <c r="AY30" s="8"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="18"/>
-    </row>
-    <row r="31" spans="1:54">
-      <c r="A31" s="35"/>
+      <c r="AS30" s="8"/>
+      <c r="AT30" s="7"/>
+      <c r="AU30" s="5"/>
+      <c r="AV30" s="5"/>
+      <c r="AW30" s="8"/>
+      <c r="AY30" s="5"/>
+      <c r="AZ30" s="18"/>
+    </row>
+    <row r="31" spans="1:52">
+      <c r="A31" s="69"/>
       <c r="B31" s="8"/>
       <c r="C31" s="7"/>
       <c r="D31" s="14" t="s">
@@ -3267,18 +3239,16 @@
       <c r="AP31" s="5"/>
       <c r="AQ31" s="8"/>
       <c r="AR31" s="7"/>
-      <c r="AS31" s="5"/>
-      <c r="AT31" s="5"/>
-      <c r="AU31" s="8"/>
-      <c r="AV31" s="7"/>
-      <c r="AW31" s="5"/>
-      <c r="AX31" s="5"/>
-      <c r="AY31" s="8"/>
-      <c r="BA31" s="5"/>
-      <c r="BB31" s="18"/>
-    </row>
-    <row r="32" spans="1:54">
-      <c r="A32" s="35"/>
+      <c r="AS31" s="8"/>
+      <c r="AT31" s="7"/>
+      <c r="AU31" s="5"/>
+      <c r="AV31" s="5"/>
+      <c r="AW31" s="8"/>
+      <c r="AY31" s="5"/>
+      <c r="AZ31" s="18"/>
+    </row>
+    <row r="32" spans="1:52">
+      <c r="A32" s="69"/>
       <c r="B32" s="8"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -3315,18 +3285,16 @@
       <c r="AP32" s="5"/>
       <c r="AQ32" s="8"/>
       <c r="AR32" s="7"/>
-      <c r="AS32" s="5"/>
-      <c r="AT32" s="5"/>
-      <c r="AU32" s="8"/>
-      <c r="AV32" s="7"/>
-      <c r="AW32" s="5"/>
-      <c r="AX32" s="5"/>
-      <c r="AY32" s="8"/>
-      <c r="BA32" s="5"/>
-      <c r="BB32" s="18"/>
-    </row>
-    <row r="33" spans="1:69">
-      <c r="A33" s="35"/>
+      <c r="AS32" s="8"/>
+      <c r="AT32" s="7"/>
+      <c r="AU32" s="5"/>
+      <c r="AV32" s="5"/>
+      <c r="AW32" s="8"/>
+      <c r="AY32" s="5"/>
+      <c r="AZ32" s="18"/>
+    </row>
+    <row r="33" spans="1:67">
+      <c r="A33" s="69"/>
       <c r="B33" s="8"/>
       <c r="C33" s="7"/>
       <c r="D33" s="5"/>
@@ -3371,18 +3339,16 @@
       <c r="AP33" s="5"/>
       <c r="AQ33" s="8"/>
       <c r="AR33" s="7"/>
-      <c r="AS33" s="5"/>
-      <c r="AT33" s="5"/>
-      <c r="AU33" s="8"/>
-      <c r="AV33" s="7"/>
-      <c r="AW33" s="5"/>
-      <c r="AX33" s="5"/>
-      <c r="AY33" s="8"/>
-      <c r="BA33" s="5"/>
-      <c r="BB33" s="18"/>
-    </row>
-    <row r="34" spans="1:69">
-      <c r="A34" s="35"/>
+      <c r="AS33" s="8"/>
+      <c r="AT33" s="7"/>
+      <c r="AU33" s="5"/>
+      <c r="AV33" s="5"/>
+      <c r="AW33" s="8"/>
+      <c r="AY33" s="5"/>
+      <c r="AZ33" s="18"/>
+    </row>
+    <row r="34" spans="1:67">
+      <c r="A34" s="69"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
       <c r="D34" s="5"/>
@@ -3427,18 +3393,16 @@
       <c r="AP34" s="5"/>
       <c r="AQ34" s="8"/>
       <c r="AR34" s="7"/>
-      <c r="AS34" s="5"/>
-      <c r="AT34" s="5"/>
-      <c r="AU34" s="8"/>
-      <c r="AV34" s="7"/>
-      <c r="AW34" s="5"/>
-      <c r="AX34" s="5"/>
-      <c r="AY34" s="8"/>
-      <c r="BA34" s="5"/>
-      <c r="BB34" s="18"/>
-    </row>
-    <row r="35" spans="1:69">
-      <c r="A35" s="35"/>
+      <c r="AS34" s="8"/>
+      <c r="AT34" s="7"/>
+      <c r="AU34" s="5"/>
+      <c r="AV34" s="5"/>
+      <c r="AW34" s="8"/>
+      <c r="AY34" s="5"/>
+      <c r="AZ34" s="18"/>
+    </row>
+    <row r="35" spans="1:67">
+      <c r="A35" s="69"/>
       <c r="B35" s="8"/>
       <c r="C35" s="7"/>
       <c r="D35" s="5"/>
@@ -3483,18 +3447,16 @@
       <c r="AP35" s="5"/>
       <c r="AQ35" s="8"/>
       <c r="AR35" s="7"/>
-      <c r="AS35" s="5"/>
-      <c r="AT35" s="5"/>
-      <c r="AU35" s="8"/>
-      <c r="AV35" s="7"/>
-      <c r="AW35" s="5"/>
-      <c r="AX35" s="5"/>
-      <c r="AY35" s="8"/>
-      <c r="BA35" s="5"/>
-      <c r="BB35" s="18"/>
-    </row>
-    <row r="36" spans="1:69">
-      <c r="A36" s="35"/>
+      <c r="AS35" s="8"/>
+      <c r="AT35" s="7"/>
+      <c r="AU35" s="5"/>
+      <c r="AV35" s="5"/>
+      <c r="AW35" s="8"/>
+      <c r="AY35" s="5"/>
+      <c r="AZ35" s="18"/>
+    </row>
+    <row r="36" spans="1:67">
+      <c r="A36" s="69"/>
       <c r="B36" s="8"/>
       <c r="C36" s="7"/>
       <c r="D36" s="5"/>
@@ -3537,17 +3499,15 @@
       <c r="AP36" s="5"/>
       <c r="AQ36" s="8"/>
       <c r="AR36" s="7"/>
-      <c r="AS36" s="5"/>
-      <c r="AT36" s="5"/>
-      <c r="AU36" s="8"/>
-      <c r="AV36" s="7"/>
-      <c r="AW36" s="5"/>
-      <c r="AX36" s="5"/>
-      <c r="AY36" s="8"/>
-      <c r="BA36" s="5"/>
-    </row>
-    <row r="37" spans="1:69">
-      <c r="A37" s="35"/>
+      <c r="AS36" s="8"/>
+      <c r="AT36" s="7"/>
+      <c r="AU36" s="5"/>
+      <c r="AV36" s="5"/>
+      <c r="AW36" s="8"/>
+      <c r="AY36" s="5"/>
+    </row>
+    <row r="37" spans="1:67">
+      <c r="A37" s="69"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
       <c r="D37" s="5"/>
@@ -3592,17 +3552,15 @@
       <c r="AP37" s="5"/>
       <c r="AQ37" s="8"/>
       <c r="AR37" s="7"/>
-      <c r="AS37" s="5"/>
-      <c r="AT37" s="5"/>
-      <c r="AU37" s="8"/>
-      <c r="AV37" s="7"/>
-      <c r="AW37" s="5"/>
-      <c r="AX37" s="5"/>
-      <c r="AY37" s="8"/>
-      <c r="BA37" s="5"/>
-    </row>
-    <row r="38" spans="1:69">
-      <c r="A38" s="35"/>
+      <c r="AS37" s="8"/>
+      <c r="AT37" s="7"/>
+      <c r="AU37" s="5"/>
+      <c r="AV37" s="5"/>
+      <c r="AW37" s="8"/>
+      <c r="AY37" s="5"/>
+    </row>
+    <row r="38" spans="1:67">
+      <c r="A38" s="69"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
       <c r="D38" s="5"/>
@@ -3647,18 +3605,16 @@
       <c r="AP38" s="5"/>
       <c r="AQ38" s="8"/>
       <c r="AR38" s="7"/>
-      <c r="AS38" s="5"/>
-      <c r="AT38" s="5"/>
-      <c r="AU38" s="8"/>
-      <c r="AV38" s="7"/>
-      <c r="AW38" s="5"/>
-      <c r="AX38" s="5"/>
-      <c r="AY38" s="8"/>
-      <c r="BA38" s="5"/>
-      <c r="BB38" s="18"/>
-    </row>
-    <row r="39" spans="1:69">
-      <c r="A39" s="35"/>
+      <c r="AS38" s="8"/>
+      <c r="AT38" s="7"/>
+      <c r="AU38" s="5"/>
+      <c r="AV38" s="5"/>
+      <c r="AW38" s="8"/>
+      <c r="AY38" s="5"/>
+      <c r="AZ38" s="18"/>
+    </row>
+    <row r="39" spans="1:67">
+      <c r="A39" s="69"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
       <c r="D39" s="5"/>
@@ -3700,19 +3656,17 @@
       <c r="AP39" s="5"/>
       <c r="AQ39" s="8"/>
       <c r="AR39" s="7"/>
-      <c r="AS39" s="5"/>
-      <c r="AT39" s="5"/>
-      <c r="AU39" s="8"/>
-      <c r="AV39" s="7"/>
-      <c r="AW39" s="5"/>
-      <c r="AX39" s="5"/>
-      <c r="AY39" s="8"/>
-      <c r="BA39" s="5"/>
-      <c r="BB39" s="18"/>
-      <c r="BP39" s="18"/>
-    </row>
-    <row r="40" spans="1:69">
-      <c r="A40" s="35"/>
+      <c r="AS39" s="8"/>
+      <c r="AT39" s="7"/>
+      <c r="AU39" s="5"/>
+      <c r="AV39" s="5"/>
+      <c r="AW39" s="8"/>
+      <c r="AY39" s="5"/>
+      <c r="AZ39" s="18"/>
+      <c r="BN39" s="18"/>
+    </row>
+    <row r="40" spans="1:67">
+      <c r="A40" s="69"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
       <c r="D40" s="5"/>
@@ -3757,19 +3711,17 @@
       <c r="AP40" s="5"/>
       <c r="AQ40" s="8"/>
       <c r="AR40" s="7"/>
-      <c r="AS40" s="5"/>
-      <c r="AT40" s="5"/>
-      <c r="AU40" s="8"/>
-      <c r="AV40" s="7"/>
-      <c r="AW40" s="5"/>
-      <c r="AX40" s="5"/>
-      <c r="AY40" s="8"/>
-      <c r="BA40" s="5"/>
-      <c r="BB40" s="18"/>
-      <c r="BP40" s="18"/>
-    </row>
-    <row r="41" spans="1:69">
-      <c r="A41" s="35"/>
+      <c r="AS40" s="8"/>
+      <c r="AT40" s="7"/>
+      <c r="AU40" s="5"/>
+      <c r="AV40" s="5"/>
+      <c r="AW40" s="8"/>
+      <c r="AY40" s="5"/>
+      <c r="AZ40" s="18"/>
+      <c r="BN40" s="18"/>
+    </row>
+    <row r="41" spans="1:67">
+      <c r="A41" s="69"/>
       <c r="B41" s="8"/>
       <c r="C41" s="7"/>
       <c r="D41" s="5"/>
@@ -3814,19 +3766,17 @@
       <c r="AP41" s="5"/>
       <c r="AQ41" s="8"/>
       <c r="AR41" s="7"/>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
-      <c r="AU41" s="8"/>
-      <c r="AV41" s="7"/>
-      <c r="AW41" s="5"/>
-      <c r="AX41" s="5"/>
-      <c r="AY41" s="8"/>
-      <c r="BA41" s="5"/>
-      <c r="BB41" s="18"/>
-      <c r="BP41" s="18"/>
-    </row>
-    <row r="42" spans="1:69">
-      <c r="A42" s="35"/>
+      <c r="AS41" s="8"/>
+      <c r="AT41" s="7"/>
+      <c r="AU41" s="5"/>
+      <c r="AV41" s="5"/>
+      <c r="AW41" s="8"/>
+      <c r="AY41" s="5"/>
+      <c r="AZ41" s="18"/>
+      <c r="BN41" s="18"/>
+    </row>
+    <row r="42" spans="1:67">
+      <c r="A42" s="69"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
       <c r="D42" s="5"/>
@@ -3871,19 +3821,17 @@
       <c r="AP42" s="5"/>
       <c r="AQ42" s="8"/>
       <c r="AR42" s="7"/>
-      <c r="AS42" s="5"/>
-      <c r="AT42" s="5"/>
-      <c r="AU42" s="8"/>
-      <c r="AV42" s="7"/>
-      <c r="AW42" s="5"/>
-      <c r="AX42" s="5"/>
-      <c r="AY42" s="8"/>
-      <c r="BA42" s="5"/>
-      <c r="BB42" s="18"/>
-      <c r="BP42" s="18"/>
-    </row>
-    <row r="43" spans="1:69">
-      <c r="A43" s="35"/>
+      <c r="AS42" s="8"/>
+      <c r="AT42" s="7"/>
+      <c r="AU42" s="5"/>
+      <c r="AV42" s="5"/>
+      <c r="AW42" s="8"/>
+      <c r="AY42" s="5"/>
+      <c r="AZ42" s="18"/>
+      <c r="BN42" s="18"/>
+    </row>
+    <row r="43" spans="1:67">
+      <c r="A43" s="69"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
       <c r="D43" s="5"/>
@@ -3928,19 +3876,17 @@
       <c r="AP43" s="5"/>
       <c r="AQ43" s="8"/>
       <c r="AR43" s="7"/>
-      <c r="AS43" s="5"/>
-      <c r="AT43" s="5"/>
-      <c r="AU43" s="8"/>
-      <c r="AV43" s="7"/>
-      <c r="AW43" s="5"/>
-      <c r="AX43" s="5"/>
-      <c r="AY43" s="8"/>
-      <c r="BA43" s="5"/>
-      <c r="BB43" s="18"/>
-      <c r="BP43" s="18"/>
-    </row>
-    <row r="44" spans="1:69">
-      <c r="A44" s="35"/>
+      <c r="AS43" s="8"/>
+      <c r="AT43" s="7"/>
+      <c r="AU43" s="5"/>
+      <c r="AV43" s="5"/>
+      <c r="AW43" s="8"/>
+      <c r="AY43" s="5"/>
+      <c r="AZ43" s="18"/>
+      <c r="BN43" s="18"/>
+    </row>
+    <row r="44" spans="1:67">
+      <c r="A44" s="69"/>
       <c r="B44" s="8"/>
       <c r="C44" s="7"/>
       <c r="D44" s="5"/>
@@ -3985,19 +3931,17 @@
       <c r="AP44" s="5"/>
       <c r="AQ44" s="8"/>
       <c r="AR44" s="7"/>
-      <c r="AS44" s="5"/>
-      <c r="AT44" s="5"/>
-      <c r="AU44" s="8"/>
-      <c r="AV44" s="7"/>
-      <c r="AW44" s="5"/>
-      <c r="AX44" s="5"/>
-      <c r="AY44" s="8"/>
-      <c r="BA44" s="5"/>
-      <c r="BB44" s="18"/>
-      <c r="BP44" s="18"/>
-    </row>
-    <row r="45" spans="1:69">
-      <c r="A45" s="35"/>
+      <c r="AS44" s="8"/>
+      <c r="AT44" s="7"/>
+      <c r="AU44" s="5"/>
+      <c r="AV44" s="5"/>
+      <c r="AW44" s="8"/>
+      <c r="AY44" s="5"/>
+      <c r="AZ44" s="18"/>
+      <c r="BN44" s="18"/>
+    </row>
+    <row r="45" spans="1:67">
+      <c r="A45" s="69"/>
       <c r="B45" s="8"/>
       <c r="C45" s="7"/>
       <c r="D45" s="5"/>
@@ -4042,19 +3986,17 @@
       <c r="AP45" s="5"/>
       <c r="AQ45" s="8"/>
       <c r="AR45" s="7"/>
-      <c r="AS45" s="5"/>
-      <c r="AT45" s="5"/>
-      <c r="AU45" s="8"/>
-      <c r="AV45" s="7"/>
-      <c r="AW45" s="5"/>
-      <c r="AX45" s="5"/>
-      <c r="AY45" s="8"/>
-      <c r="BA45" s="5"/>
-      <c r="BB45" s="18"/>
-      <c r="BP45" s="18"/>
-    </row>
-    <row r="46" spans="1:69">
-      <c r="A46" s="35"/>
+      <c r="AS45" s="8"/>
+      <c r="AT45" s="7"/>
+      <c r="AU45" s="5"/>
+      <c r="AV45" s="5"/>
+      <c r="AW45" s="8"/>
+      <c r="AY45" s="5"/>
+      <c r="AZ45" s="18"/>
+      <c r="BN45" s="18"/>
+    </row>
+    <row r="46" spans="1:67">
+      <c r="A46" s="69"/>
       <c r="B46" s="8"/>
       <c r="C46" s="7"/>
       <c r="D46" s="5"/>
@@ -4099,19 +4041,17 @@
       <c r="AP46" s="5"/>
       <c r="AQ46" s="8"/>
       <c r="AR46" s="7"/>
-      <c r="AS46" s="5"/>
-      <c r="AT46" s="5"/>
-      <c r="AU46" s="8"/>
-      <c r="AV46" s="7"/>
-      <c r="AW46" s="5"/>
-      <c r="AX46" s="5"/>
-      <c r="AY46" s="8"/>
-      <c r="BA46" s="5"/>
-      <c r="BB46" s="18"/>
-      <c r="BP46" s="18"/>
-    </row>
-    <row r="47" spans="1:69">
-      <c r="A47" s="35"/>
+      <c r="AS46" s="8"/>
+      <c r="AT46" s="7"/>
+      <c r="AU46" s="5"/>
+      <c r="AV46" s="5"/>
+      <c r="AW46" s="8"/>
+      <c r="AY46" s="5"/>
+      <c r="AZ46" s="18"/>
+      <c r="BN46" s="18"/>
+    </row>
+    <row r="47" spans="1:67">
+      <c r="A47" s="69"/>
       <c r="B47" s="8"/>
       <c r="C47" s="7"/>
       <c r="D47" s="5"/>
@@ -4156,20 +4096,18 @@
       <c r="AP47" s="5"/>
       <c r="AQ47" s="8"/>
       <c r="AR47" s="7"/>
-      <c r="AS47" s="5"/>
-      <c r="AT47" s="5"/>
-      <c r="AU47" s="8"/>
-      <c r="AV47" s="7"/>
-      <c r="AW47" s="5"/>
-      <c r="AX47" s="5"/>
-      <c r="AY47" s="8"/>
-      <c r="BA47" s="5"/>
-      <c r="BB47" s="18"/>
-      <c r="BP47" s="18"/>
-      <c r="BQ47" s="5"/>
-    </row>
-    <row r="48" spans="1:69">
-      <c r="A48" s="35"/>
+      <c r="AS47" s="8"/>
+      <c r="AT47" s="7"/>
+      <c r="AU47" s="5"/>
+      <c r="AV47" s="5"/>
+      <c r="AW47" s="8"/>
+      <c r="AY47" s="5"/>
+      <c r="AZ47" s="18"/>
+      <c r="BN47" s="18"/>
+      <c r="BO47" s="5"/>
+    </row>
+    <row r="48" spans="1:67">
+      <c r="A48" s="69"/>
       <c r="B48" s="8"/>
       <c r="C48" s="7"/>
       <c r="D48" s="5"/>
@@ -4214,20 +4152,18 @@
       <c r="AP48" s="5"/>
       <c r="AQ48" s="8"/>
       <c r="AR48" s="7"/>
-      <c r="AS48" s="5"/>
-      <c r="AT48" s="5"/>
-      <c r="AU48" s="8"/>
-      <c r="AV48" s="7"/>
-      <c r="AW48" s="5"/>
-      <c r="AX48" s="5"/>
-      <c r="AY48" s="8"/>
-      <c r="BA48" s="5"/>
-      <c r="BB48" s="18"/>
-      <c r="BP48" s="18"/>
-      <c r="BQ48" s="5"/>
-    </row>
-    <row r="49" spans="1:69">
-      <c r="A49" s="35"/>
+      <c r="AS48" s="8"/>
+      <c r="AT48" s="7"/>
+      <c r="AU48" s="5"/>
+      <c r="AV48" s="5"/>
+      <c r="AW48" s="8"/>
+      <c r="AY48" s="5"/>
+      <c r="AZ48" s="18"/>
+      <c r="BN48" s="18"/>
+      <c r="BO48" s="5"/>
+    </row>
+    <row r="49" spans="1:67">
+      <c r="A49" s="69"/>
       <c r="B49" s="8"/>
       <c r="C49" s="7"/>
       <c r="D49" s="5"/>
@@ -4270,20 +4206,18 @@
       <c r="AP49" s="5"/>
       <c r="AQ49" s="8"/>
       <c r="AR49" s="7"/>
-      <c r="AS49" s="5"/>
-      <c r="AT49" s="5"/>
-      <c r="AU49" s="8"/>
-      <c r="AV49" s="7"/>
-      <c r="AW49" s="5"/>
-      <c r="AX49" s="5"/>
-      <c r="AY49" s="8"/>
-      <c r="BA49" s="5"/>
+      <c r="AS49" s="8"/>
+      <c r="AT49" s="7"/>
+      <c r="AU49" s="5"/>
+      <c r="AV49" s="5"/>
+      <c r="AW49" s="8"/>
+      <c r="AY49" s="5"/>
+      <c r="BM49" s="5"/>
+      <c r="BN49" s="5"/>
       <c r="BO49" s="5"/>
-      <c r="BP49" s="5"/>
-      <c r="BQ49" s="5"/>
-    </row>
-    <row r="50" spans="1:69">
-      <c r="A50" s="35"/>
+    </row>
+    <row r="50" spans="1:67">
+      <c r="A50" s="69"/>
       <c r="B50" s="8"/>
       <c r="C50" s="7"/>
       <c r="D50" s="5"/>
@@ -4328,20 +4262,18 @@
       <c r="AP50" s="5"/>
       <c r="AQ50" s="8"/>
       <c r="AR50" s="7"/>
-      <c r="AS50" s="5"/>
-      <c r="AT50" s="5"/>
-      <c r="AU50" s="8"/>
-      <c r="AV50" s="7"/>
-      <c r="AW50" s="5"/>
-      <c r="AX50" s="5"/>
-      <c r="AY50" s="8"/>
-      <c r="BA50" s="5"/>
+      <c r="AS50" s="8"/>
+      <c r="AT50" s="7"/>
+      <c r="AU50" s="5"/>
+      <c r="AV50" s="5"/>
+      <c r="AW50" s="8"/>
+      <c r="AY50" s="5"/>
+      <c r="BM50" s="5"/>
+      <c r="BN50" s="5"/>
       <c r="BO50" s="5"/>
-      <c r="BP50" s="5"/>
-      <c r="BQ50" s="5"/>
-    </row>
-    <row r="51" spans="1:69">
-      <c r="A51" s="35"/>
+    </row>
+    <row r="51" spans="1:67">
+      <c r="A51" s="69"/>
       <c r="B51" s="8"/>
       <c r="C51" s="7"/>
       <c r="D51" s="5"/>
@@ -4384,20 +4316,18 @@
       <c r="AP51" s="5"/>
       <c r="AQ51" s="8"/>
       <c r="AR51" s="7"/>
-      <c r="AS51" s="5"/>
-      <c r="AT51" s="5"/>
-      <c r="AU51" s="8"/>
-      <c r="AV51" s="7"/>
-      <c r="AW51" s="5"/>
-      <c r="AX51" s="5"/>
-      <c r="AY51" s="8"/>
-      <c r="BA51" s="5"/>
+      <c r="AS51" s="8"/>
+      <c r="AT51" s="7"/>
+      <c r="AU51" s="5"/>
+      <c r="AV51" s="5"/>
+      <c r="AW51" s="8"/>
+      <c r="AY51" s="5"/>
+      <c r="BM51" s="5"/>
+      <c r="BN51" s="5"/>
       <c r="BO51" s="5"/>
-      <c r="BP51" s="5"/>
-      <c r="BQ51" s="5"/>
-    </row>
-    <row r="52" spans="1:69">
-      <c r="A52" s="35"/>
+    </row>
+    <row r="52" spans="1:67">
+      <c r="A52" s="69"/>
       <c r="B52" s="8"/>
       <c r="C52" s="7"/>
       <c r="D52" s="5"/>
@@ -4442,17 +4372,15 @@
       <c r="AP52" s="5"/>
       <c r="AQ52" s="8"/>
       <c r="AR52" s="7"/>
-      <c r="AS52" s="5"/>
-      <c r="AT52" s="5"/>
-      <c r="AU52" s="8"/>
-      <c r="AV52" s="7"/>
-      <c r="AW52" s="5"/>
-      <c r="AX52" s="5"/>
-      <c r="AY52" s="8"/>
-      <c r="BA52" s="5"/>
-    </row>
-    <row r="53" spans="1:69">
-      <c r="A53" s="35"/>
+      <c r="AS52" s="8"/>
+      <c r="AT52" s="7"/>
+      <c r="AU52" s="5"/>
+      <c r="AV52" s="5"/>
+      <c r="AW52" s="8"/>
+      <c r="AY52" s="5"/>
+    </row>
+    <row r="53" spans="1:67">
+      <c r="A53" s="69"/>
       <c r="B53" s="8"/>
       <c r="C53" s="7"/>
       <c r="D53" s="5"/>
@@ -4497,17 +4425,15 @@
       <c r="AP53" s="5"/>
       <c r="AQ53" s="8"/>
       <c r="AR53" s="7"/>
-      <c r="AS53" s="5"/>
-      <c r="AT53" s="5"/>
-      <c r="AU53" s="8"/>
-      <c r="AV53" s="7"/>
-      <c r="AW53" s="5"/>
-      <c r="AX53" s="5"/>
-      <c r="AY53" s="8"/>
-      <c r="BA53" s="5"/>
-    </row>
-    <row r="54" spans="1:69">
-      <c r="A54" s="35"/>
+      <c r="AS53" s="8"/>
+      <c r="AT53" s="7"/>
+      <c r="AU53" s="5"/>
+      <c r="AV53" s="5"/>
+      <c r="AW53" s="8"/>
+      <c r="AY53" s="5"/>
+    </row>
+    <row r="54" spans="1:67">
+      <c r="A54" s="69"/>
       <c r="B54" s="8"/>
       <c r="C54" s="7"/>
       <c r="D54" s="5"/>
@@ -4552,18 +4478,16 @@
       <c r="AP54" s="5"/>
       <c r="AQ54" s="8"/>
       <c r="AR54" s="7"/>
-      <c r="AS54" s="5"/>
-      <c r="AT54" s="5"/>
-      <c r="AU54" s="8"/>
-      <c r="AV54" s="7"/>
-      <c r="AW54" s="5"/>
-      <c r="AX54" s="5"/>
-      <c r="AY54" s="8"/>
-      <c r="BA54" s="5"/>
-      <c r="BB54" s="18"/>
-    </row>
-    <row r="55" spans="1:69">
-      <c r="A55" s="35"/>
+      <c r="AS54" s="8"/>
+      <c r="AT54" s="7"/>
+      <c r="AU54" s="5"/>
+      <c r="AV54" s="5"/>
+      <c r="AW54" s="8"/>
+      <c r="AY54" s="5"/>
+      <c r="AZ54" s="18"/>
+    </row>
+    <row r="55" spans="1:67">
+      <c r="A55" s="69"/>
       <c r="B55" s="8"/>
       <c r="C55" s="7"/>
       <c r="D55" s="5"/>
@@ -4608,21 +4532,19 @@
       <c r="AP55" s="5"/>
       <c r="AQ55" s="8"/>
       <c r="AR55" s="7"/>
-      <c r="AS55" s="5"/>
-      <c r="AT55" s="5"/>
-      <c r="AU55" s="8"/>
-      <c r="AV55" s="7"/>
-      <c r="AW55" s="5"/>
-      <c r="AX55" s="5"/>
-      <c r="AY55" s="8"/>
-      <c r="BA55" s="5"/>
-      <c r="BB55" s="18"/>
+      <c r="AS55" s="8"/>
+      <c r="AT55" s="7"/>
+      <c r="AU55" s="5"/>
+      <c r="AV55" s="5"/>
+      <c r="AW55" s="8"/>
+      <c r="AY55" s="5"/>
+      <c r="AZ55" s="18"/>
+      <c r="BE55" s="5"/>
+      <c r="BF55" s="5"/>
       <c r="BG55" s="5"/>
-      <c r="BH55" s="5"/>
-      <c r="BI55" s="5"/>
-    </row>
-    <row r="56" spans="1:69">
-      <c r="A56" s="35"/>
+    </row>
+    <row r="56" spans="1:67">
+      <c r="A56" s="69"/>
       <c r="B56" s="8"/>
       <c r="C56" s="7"/>
       <c r="D56" s="5"/>
@@ -4667,21 +4589,19 @@
       <c r="AP56" s="5"/>
       <c r="AQ56" s="8"/>
       <c r="AR56" s="7"/>
-      <c r="AS56" s="5"/>
-      <c r="AT56" s="5"/>
-      <c r="AU56" s="8"/>
-      <c r="AV56" s="7"/>
-      <c r="AW56" s="5"/>
-      <c r="AX56" s="5"/>
-      <c r="AY56" s="8"/>
-      <c r="BA56" s="5"/>
-      <c r="BB56" s="18"/>
-      <c r="BG56" s="5"/>
-      <c r="BH56" s="26"/>
-      <c r="BI56" s="26"/>
-    </row>
-    <row r="57" spans="1:69">
-      <c r="A57" s="35"/>
+      <c r="AS56" s="8"/>
+      <c r="AT56" s="7"/>
+      <c r="AU56" s="5"/>
+      <c r="AV56" s="5"/>
+      <c r="AW56" s="8"/>
+      <c r="AY56" s="5"/>
+      <c r="AZ56" s="18"/>
+      <c r="BE56" s="5"/>
+      <c r="BF56" s="26"/>
+      <c r="BG56" s="26"/>
+    </row>
+    <row r="57" spans="1:67">
+      <c r="A57" s="69"/>
       <c r="B57" s="8"/>
       <c r="C57" s="7"/>
       <c r="D57" s="5"/>
@@ -4726,21 +4646,19 @@
       <c r="AP57" s="5"/>
       <c r="AQ57" s="8"/>
       <c r="AR57" s="7"/>
-      <c r="AS57" s="5"/>
-      <c r="AT57" s="5"/>
-      <c r="AU57" s="8"/>
-      <c r="AV57" s="7"/>
-      <c r="AW57" s="5"/>
-      <c r="AX57" s="5"/>
-      <c r="AY57" s="8"/>
-      <c r="BA57" s="5"/>
-      <c r="BB57" s="18"/>
-      <c r="BG57" s="5"/>
-      <c r="BH57" s="26"/>
-      <c r="BI57" s="26"/>
-    </row>
-    <row r="58" spans="1:69">
-      <c r="A58" s="35"/>
+      <c r="AS57" s="8"/>
+      <c r="AT57" s="7"/>
+      <c r="AU57" s="5"/>
+      <c r="AV57" s="5"/>
+      <c r="AW57" s="8"/>
+      <c r="AY57" s="5"/>
+      <c r="AZ57" s="18"/>
+      <c r="BE57" s="5"/>
+      <c r="BF57" s="26"/>
+      <c r="BG57" s="26"/>
+    </row>
+    <row r="58" spans="1:67">
+      <c r="A58" s="69"/>
       <c r="B58" s="8"/>
       <c r="C58" s="7"/>
       <c r="D58" s="5"/>
@@ -4785,20 +4703,18 @@
       <c r="AP58" s="5"/>
       <c r="AQ58" s="8"/>
       <c r="AR58" s="7"/>
-      <c r="AS58" s="5"/>
-      <c r="AT58" s="5"/>
-      <c r="AU58" s="8"/>
-      <c r="AV58" s="7"/>
-      <c r="AW58" s="5"/>
-      <c r="AX58" s="5"/>
-      <c r="AY58" s="8"/>
-      <c r="BA58" s="5"/>
-      <c r="BB58" s="18"/>
-      <c r="BG58" s="5"/>
-      <c r="BH58" s="26"/>
-      <c r="BI58" s="26"/>
-    </row>
-    <row r="59" spans="1:69">
+      <c r="AS58" s="8"/>
+      <c r="AT58" s="7"/>
+      <c r="AU58" s="5"/>
+      <c r="AV58" s="5"/>
+      <c r="AW58" s="8"/>
+      <c r="AY58" s="5"/>
+      <c r="AZ58" s="18"/>
+      <c r="BE58" s="5"/>
+      <c r="BF58" s="26"/>
+      <c r="BG58" s="26"/>
+    </row>
+    <row r="59" spans="1:67">
       <c r="A59" s="1"/>
       <c r="B59" s="8"/>
       <c r="C59" s="7"/>
@@ -4844,21 +4760,19 @@
       <c r="AP59" s="5"/>
       <c r="AQ59" s="8"/>
       <c r="AR59" s="7"/>
-      <c r="AS59" s="5"/>
-      <c r="AT59" s="5"/>
-      <c r="AU59" s="8"/>
-      <c r="AV59" s="7"/>
-      <c r="AW59" s="5"/>
-      <c r="AX59" s="5"/>
-      <c r="AY59" s="8"/>
-      <c r="BA59" s="5"/>
-      <c r="BB59" s="18"/>
-      <c r="BG59" s="5"/>
-      <c r="BH59" s="26"/>
-      <c r="BI59" s="26"/>
-    </row>
-    <row r="60" spans="1:69">
-      <c r="A60" s="61" t="s">
+      <c r="AS59" s="8"/>
+      <c r="AT59" s="7"/>
+      <c r="AU59" s="5"/>
+      <c r="AV59" s="5"/>
+      <c r="AW59" s="8"/>
+      <c r="AY59" s="5"/>
+      <c r="AZ59" s="18"/>
+      <c r="BE59" s="5"/>
+      <c r="BF59" s="26"/>
+      <c r="BG59" s="26"/>
+    </row>
+    <row r="60" spans="1:67" ht="18">
+      <c r="A60" s="35" t="s">
         <v>59</v>
       </c>
       <c r="B60" s="23"/>
@@ -4903,22 +4817,24 @@
       <c r="AO60" s="4"/>
       <c r="AP60" s="4"/>
       <c r="AQ60" s="23"/>
-      <c r="AR60" s="24"/>
-      <c r="AS60" s="4"/>
-      <c r="AT60" s="4"/>
-      <c r="AU60" s="23"/>
-      <c r="AV60" s="24"/>
-      <c r="AW60" s="4"/>
-      <c r="AX60" s="4"/>
-      <c r="AY60" s="23"/>
-      <c r="BA60" s="5"/>
-      <c r="BB60" s="18"/>
-      <c r="BG60" s="5"/>
-      <c r="BH60" s="26"/>
-      <c r="BI60" s="26"/>
-    </row>
-    <row r="61" spans="1:69">
-      <c r="A61" s="62"/>
+      <c r="AR60" s="71">
+        <v>45594</v>
+      </c>
+      <c r="AS60" s="23"/>
+      <c r="AT60" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU60" s="4"/>
+      <c r="AV60" s="4"/>
+      <c r="AW60" s="23"/>
+      <c r="AY60" s="5"/>
+      <c r="AZ60" s="18"/>
+      <c r="BE60" s="5"/>
+      <c r="BF60" s="26"/>
+      <c r="BG60" s="26"/>
+    </row>
+    <row r="61" spans="1:67">
+      <c r="A61" s="36"/>
       <c r="B61" s="8"/>
       <c r="C61" s="13" t="s">
         <v>29</v>
@@ -4965,21 +4881,19 @@
       <c r="AP61" s="5"/>
       <c r="AQ61" s="8"/>
       <c r="AR61" s="7"/>
-      <c r="AS61" s="5"/>
-      <c r="AT61" s="5"/>
-      <c r="AU61" s="8"/>
-      <c r="AV61" s="7"/>
-      <c r="AW61" s="5"/>
-      <c r="AX61" s="5"/>
-      <c r="AY61" s="8"/>
-      <c r="BA61" s="5"/>
-      <c r="BB61" s="18"/>
-      <c r="BG61" s="5"/>
-      <c r="BH61" s="26"/>
-      <c r="BI61" s="26"/>
-    </row>
-    <row r="62" spans="1:69">
-      <c r="A62" s="62"/>
+      <c r="AS61" s="8"/>
+      <c r="AT61" s="7"/>
+      <c r="AU61" s="5"/>
+      <c r="AV61" s="5"/>
+      <c r="AW61" s="8"/>
+      <c r="AY61" s="5"/>
+      <c r="AZ61" s="18"/>
+      <c r="BE61" s="5"/>
+      <c r="BF61" s="26"/>
+      <c r="BG61" s="26"/>
+    </row>
+    <row r="62" spans="1:67">
+      <c r="A62" s="36"/>
       <c r="B62" s="8">
         <v>1</v>
       </c>
@@ -5028,21 +4942,19 @@
       <c r="AP62" s="5"/>
       <c r="AQ62" s="8"/>
       <c r="AR62" s="7"/>
-      <c r="AS62" s="5"/>
-      <c r="AT62" s="5"/>
-      <c r="AU62" s="8"/>
-      <c r="AV62" s="7"/>
-      <c r="AW62" s="5"/>
-      <c r="AX62" s="5"/>
-      <c r="AY62" s="8"/>
-      <c r="BA62" s="5"/>
-      <c r="BB62" s="18"/>
-      <c r="BG62" s="5"/>
-      <c r="BH62" s="26"/>
-      <c r="BI62" s="26"/>
-    </row>
-    <row r="63" spans="1:69">
-      <c r="A63" s="62"/>
+      <c r="AS62" s="8"/>
+      <c r="AT62" s="7"/>
+      <c r="AU62" s="5"/>
+      <c r="AV62" s="5"/>
+      <c r="AW62" s="8"/>
+      <c r="AY62" s="5"/>
+      <c r="AZ62" s="18"/>
+      <c r="BE62" s="5"/>
+      <c r="BF62" s="26"/>
+      <c r="BG62" s="26"/>
+    </row>
+    <row r="63" spans="1:67">
+      <c r="A63" s="36"/>
       <c r="B63" s="8">
         <v>2</v>
       </c>
@@ -5089,21 +5001,19 @@
       <c r="AP63" s="5"/>
       <c r="AQ63" s="8"/>
       <c r="AR63" s="7"/>
-      <c r="AS63" s="5"/>
-      <c r="AT63" s="5"/>
-      <c r="AU63" s="8"/>
-      <c r="AV63" s="7"/>
-      <c r="AW63" s="5"/>
-      <c r="AX63" s="5"/>
-      <c r="AY63" s="8"/>
-      <c r="BA63" s="5"/>
-      <c r="BB63" s="18"/>
-      <c r="BG63" s="5"/>
-      <c r="BH63" s="26"/>
-      <c r="BI63" s="26"/>
-    </row>
-    <row r="64" spans="1:69">
-      <c r="A64" s="62"/>
+      <c r="AS63" s="8"/>
+      <c r="AT63" s="7"/>
+      <c r="AU63" s="5"/>
+      <c r="AV63" s="5"/>
+      <c r="AW63" s="8"/>
+      <c r="AY63" s="5"/>
+      <c r="AZ63" s="18"/>
+      <c r="BE63" s="5"/>
+      <c r="BF63" s="26"/>
+      <c r="BG63" s="26"/>
+    </row>
+    <row r="64" spans="1:67">
+      <c r="A64" s="36"/>
       <c r="B64" s="8"/>
       <c r="C64" s="7"/>
       <c r="D64" s="5"/>
@@ -5148,19 +5058,17 @@
       <c r="AP64" s="5"/>
       <c r="AQ64" s="8"/>
       <c r="AR64" s="7"/>
-      <c r="AS64" s="5"/>
-      <c r="AT64" s="5"/>
-      <c r="AU64" s="8"/>
-      <c r="AV64" s="7"/>
-      <c r="AW64" s="5"/>
-      <c r="AX64" s="5"/>
-      <c r="AY64" s="8"/>
-      <c r="BG64" s="5"/>
-      <c r="BH64" s="26"/>
-      <c r="BI64" s="26"/>
-    </row>
-    <row r="65" spans="1:61">
-      <c r="A65" s="62"/>
+      <c r="AS64" s="8"/>
+      <c r="AT64" s="7"/>
+      <c r="AU64" s="5"/>
+      <c r="AV64" s="5"/>
+      <c r="AW64" s="8"/>
+      <c r="BE64" s="5"/>
+      <c r="BF64" s="26"/>
+      <c r="BG64" s="26"/>
+    </row>
+    <row r="65" spans="1:59">
+      <c r="A65" s="36"/>
       <c r="B65" s="8"/>
       <c r="C65" s="7"/>
       <c r="D65" s="14" t="s">
@@ -5207,19 +5115,17 @@
       <c r="AP65" s="5"/>
       <c r="AQ65" s="8"/>
       <c r="AR65" s="7"/>
-      <c r="AS65" s="5"/>
-      <c r="AT65" s="5"/>
-      <c r="AU65" s="8"/>
-      <c r="AV65" s="7"/>
-      <c r="AW65" s="5"/>
-      <c r="AX65" s="5"/>
-      <c r="AY65" s="8"/>
-      <c r="BG65" s="5"/>
-      <c r="BH65" s="26"/>
-      <c r="BI65" s="26"/>
-    </row>
-    <row r="66" spans="1:61">
-      <c r="A66" s="62"/>
+      <c r="AS65" s="8"/>
+      <c r="AT65" s="7"/>
+      <c r="AU65" s="5"/>
+      <c r="AV65" s="5"/>
+      <c r="AW65" s="8"/>
+      <c r="BE65" s="5"/>
+      <c r="BF65" s="26"/>
+      <c r="BG65" s="26"/>
+    </row>
+    <row r="66" spans="1:59">
+      <c r="A66" s="36"/>
       <c r="B66" s="8"/>
       <c r="C66" s="7"/>
       <c r="D66" s="5"/>
@@ -5262,19 +5168,17 @@
       <c r="AP66" s="5"/>
       <c r="AQ66" s="8"/>
       <c r="AR66" s="7"/>
-      <c r="AS66" s="5"/>
-      <c r="AT66" s="5"/>
-      <c r="AU66" s="8"/>
-      <c r="AV66" s="7"/>
-      <c r="AW66" s="5"/>
-      <c r="AX66" s="5"/>
-      <c r="AY66" s="8"/>
-      <c r="BG66" s="5"/>
-      <c r="BH66" s="26"/>
-      <c r="BI66" s="26"/>
-    </row>
-    <row r="67" spans="1:61">
-      <c r="A67" s="62"/>
+      <c r="AS66" s="8"/>
+      <c r="AT66" s="7"/>
+      <c r="AU66" s="5"/>
+      <c r="AV66" s="5"/>
+      <c r="AW66" s="8"/>
+      <c r="BE66" s="5"/>
+      <c r="BF66" s="26"/>
+      <c r="BG66" s="26"/>
+    </row>
+    <row r="67" spans="1:59">
+      <c r="A67" s="36"/>
       <c r="B67" s="8"/>
       <c r="C67" s="7"/>
       <c r="D67" s="5"/>
@@ -5319,19 +5223,17 @@
       <c r="AP67" s="5"/>
       <c r="AQ67" s="8"/>
       <c r="AR67" s="7"/>
-      <c r="AS67" s="5"/>
-      <c r="AT67" s="5"/>
-      <c r="AU67" s="8"/>
-      <c r="AV67" s="7"/>
-      <c r="AW67" s="5"/>
-      <c r="AX67" s="5"/>
-      <c r="AY67" s="8"/>
-      <c r="BG67" s="5"/>
-      <c r="BH67" s="26"/>
-      <c r="BI67" s="26"/>
-    </row>
-    <row r="68" spans="1:61">
-      <c r="A68" s="62"/>
+      <c r="AS67" s="8"/>
+      <c r="AT67" s="7"/>
+      <c r="AU67" s="5"/>
+      <c r="AV67" s="5"/>
+      <c r="AW67" s="8"/>
+      <c r="BE67" s="5"/>
+      <c r="BF67" s="26"/>
+      <c r="BG67" s="26"/>
+    </row>
+    <row r="68" spans="1:59">
+      <c r="A68" s="36"/>
       <c r="B68" s="8"/>
       <c r="C68" s="7"/>
       <c r="D68" s="5"/>
@@ -5376,19 +5278,17 @@
       <c r="AP68" s="5"/>
       <c r="AQ68" s="8"/>
       <c r="AR68" s="7"/>
-      <c r="AS68" s="5"/>
-      <c r="AT68" s="5"/>
-      <c r="AU68" s="8"/>
-      <c r="AV68" s="7"/>
-      <c r="AW68" s="5"/>
-      <c r="AX68" s="5"/>
-      <c r="AY68" s="8"/>
-      <c r="BG68" s="5"/>
-      <c r="BH68" s="26"/>
-      <c r="BI68" s="26"/>
-    </row>
-    <row r="69" spans="1:61">
-      <c r="A69" s="62"/>
+      <c r="AS68" s="8"/>
+      <c r="AT68" s="7"/>
+      <c r="AU68" s="5"/>
+      <c r="AV68" s="5"/>
+      <c r="AW68" s="8"/>
+      <c r="BE68" s="5"/>
+      <c r="BF68" s="26"/>
+      <c r="BG68" s="26"/>
+    </row>
+    <row r="69" spans="1:59">
+      <c r="A69" s="36"/>
       <c r="B69" s="8"/>
       <c r="C69" s="7"/>
       <c r="D69" s="5"/>
@@ -5433,19 +5333,17 @@
       <c r="AP69" s="5"/>
       <c r="AQ69" s="8"/>
       <c r="AR69" s="7"/>
-      <c r="AS69" s="5"/>
-      <c r="AT69" s="5"/>
-      <c r="AU69" s="8"/>
-      <c r="AV69" s="7"/>
-      <c r="AW69" s="5"/>
-      <c r="AX69" s="5"/>
-      <c r="AY69" s="8"/>
-      <c r="BG69" s="5"/>
-      <c r="BH69" s="26"/>
-      <c r="BI69" s="26"/>
-    </row>
-    <row r="70" spans="1:61">
-      <c r="A70" s="62"/>
+      <c r="AS69" s="8"/>
+      <c r="AT69" s="7"/>
+      <c r="AU69" s="5"/>
+      <c r="AV69" s="5"/>
+      <c r="AW69" s="8"/>
+      <c r="BE69" s="5"/>
+      <c r="BF69" s="26"/>
+      <c r="BG69" s="26"/>
+    </row>
+    <row r="70" spans="1:59">
+      <c r="A70" s="36"/>
       <c r="B70" s="8"/>
       <c r="C70" s="7"/>
       <c r="D70" s="5"/>
@@ -5488,20 +5386,18 @@
       <c r="AP70" s="5"/>
       <c r="AQ70" s="8"/>
       <c r="AR70" s="7"/>
-      <c r="AS70" s="5"/>
-      <c r="AT70" s="5"/>
-      <c r="AU70" s="8"/>
-      <c r="AV70" s="7"/>
-      <c r="AW70" s="5"/>
+      <c r="AS70" s="8"/>
+      <c r="AT70" s="7"/>
+      <c r="AU70" s="5"/>
+      <c r="AV70" s="5"/>
+      <c r="AW70" s="8"/>
       <c r="AX70" s="5"/>
-      <c r="AY70" s="8"/>
-      <c r="AZ70" s="5"/>
-      <c r="BG70" s="5"/>
-      <c r="BH70" s="26"/>
-      <c r="BI70" s="26"/>
-    </row>
-    <row r="71" spans="1:61">
-      <c r="A71" s="62"/>
+      <c r="BE70" s="5"/>
+      <c r="BF70" s="26"/>
+      <c r="BG70" s="26"/>
+    </row>
+    <row r="71" spans="1:59">
+      <c r="A71" s="36"/>
       <c r="B71" s="8"/>
       <c r="C71" s="7"/>
       <c r="D71" s="5"/>
@@ -5546,19 +5442,17 @@
       <c r="AP71" s="5"/>
       <c r="AQ71" s="8"/>
       <c r="AR71" s="7"/>
-      <c r="AS71" s="5"/>
-      <c r="AT71" s="5"/>
-      <c r="AU71" s="8"/>
-      <c r="AV71" s="7"/>
-      <c r="AW71" s="5"/>
-      <c r="AX71" s="5"/>
-      <c r="AY71" s="8"/>
-      <c r="BG71" s="5"/>
-      <c r="BH71" s="26"/>
-      <c r="BI71" s="26"/>
-    </row>
-    <row r="72" spans="1:61">
-      <c r="A72" s="62"/>
+      <c r="AS71" s="8"/>
+      <c r="AT71" s="7"/>
+      <c r="AU71" s="5"/>
+      <c r="AV71" s="5"/>
+      <c r="AW71" s="8"/>
+      <c r="BE71" s="5"/>
+      <c r="BF71" s="26"/>
+      <c r="BG71" s="26"/>
+    </row>
+    <row r="72" spans="1:59">
+      <c r="A72" s="36"/>
       <c r="B72" s="8"/>
       <c r="C72" s="7"/>
       <c r="D72" s="5"/>
@@ -5603,19 +5497,17 @@
       <c r="AP72" s="5"/>
       <c r="AQ72" s="8"/>
       <c r="AR72" s="7"/>
-      <c r="AS72" s="5"/>
-      <c r="AT72" s="5"/>
-      <c r="AU72" s="8"/>
-      <c r="AV72" s="7"/>
-      <c r="AW72" s="5"/>
-      <c r="AX72" s="5"/>
-      <c r="AY72" s="8"/>
-      <c r="BG72" s="5"/>
-      <c r="BH72" s="26"/>
-      <c r="BI72" s="26"/>
-    </row>
-    <row r="73" spans="1:61">
-      <c r="A73" s="62"/>
+      <c r="AS72" s="8"/>
+      <c r="AT72" s="7"/>
+      <c r="AU72" s="5"/>
+      <c r="AV72" s="5"/>
+      <c r="AW72" s="8"/>
+      <c r="BE72" s="5"/>
+      <c r="BF72" s="26"/>
+      <c r="BG72" s="26"/>
+    </row>
+    <row r="73" spans="1:59">
+      <c r="A73" s="36"/>
       <c r="B73" s="8"/>
       <c r="C73" s="7"/>
       <c r="D73" s="5"/>
@@ -5657,19 +5549,17 @@
       <c r="AP73" s="5"/>
       <c r="AQ73" s="8"/>
       <c r="AR73" s="7"/>
-      <c r="AS73" s="5"/>
-      <c r="AT73" s="5"/>
-      <c r="AU73" s="8"/>
-      <c r="AV73" s="7"/>
-      <c r="AW73" s="5"/>
-      <c r="AX73" s="5"/>
-      <c r="AY73" s="8"/>
-      <c r="BG73" s="5"/>
-      <c r="BH73" s="26"/>
-      <c r="BI73" s="26"/>
-    </row>
-    <row r="74" spans="1:61">
-      <c r="A74" s="62"/>
+      <c r="AS73" s="8"/>
+      <c r="AT73" s="7"/>
+      <c r="AU73" s="5"/>
+      <c r="AV73" s="5"/>
+      <c r="AW73" s="8"/>
+      <c r="BE73" s="5"/>
+      <c r="BF73" s="26"/>
+      <c r="BG73" s="26"/>
+    </row>
+    <row r="74" spans="1:59">
+      <c r="A74" s="36"/>
       <c r="B74" s="8"/>
       <c r="C74" s="7"/>
       <c r="D74" s="5"/>
@@ -5714,19 +5604,17 @@
       <c r="AP74" s="5"/>
       <c r="AQ74" s="8"/>
       <c r="AR74" s="7"/>
-      <c r="AS74" s="5"/>
-      <c r="AT74" s="5"/>
-      <c r="AU74" s="8"/>
-      <c r="AV74" s="7"/>
-      <c r="AW74" s="5"/>
-      <c r="AX74" s="5"/>
-      <c r="AY74" s="8"/>
-      <c r="BG74" s="5"/>
-      <c r="BH74" s="26"/>
-      <c r="BI74" s="26"/>
-    </row>
-    <row r="75" spans="1:61">
-      <c r="A75" s="62"/>
+      <c r="AS74" s="8"/>
+      <c r="AT74" s="7"/>
+      <c r="AU74" s="5"/>
+      <c r="AV74" s="5"/>
+      <c r="AW74" s="8"/>
+      <c r="BE74" s="5"/>
+      <c r="BF74" s="26"/>
+      <c r="BG74" s="26"/>
+    </row>
+    <row r="75" spans="1:59">
+      <c r="A75" s="36"/>
       <c r="B75" s="8"/>
       <c r="C75" s="7"/>
       <c r="D75" s="5"/>
@@ -5750,7 +5638,7 @@
       <c r="V75" s="8"/>
       <c r="X75" s="16"/>
       <c r="Y75" s="7"/>
-      <c r="Z75" s="59" t="s">
+      <c r="Z75" s="30" t="s">
         <v>24</v>
       </c>
       <c r="AA75" s="5"/>
@@ -5771,19 +5659,17 @@
       <c r="AP75" s="5"/>
       <c r="AQ75" s="8"/>
       <c r="AR75" s="7"/>
-      <c r="AS75" s="5"/>
-      <c r="AT75" s="5"/>
-      <c r="AU75" s="8"/>
-      <c r="AV75" s="7"/>
-      <c r="AW75" s="5"/>
-      <c r="AX75" s="5"/>
-      <c r="AY75" s="8"/>
-      <c r="BG75" s="5"/>
-      <c r="BH75" s="26"/>
-      <c r="BI75" s="26"/>
-    </row>
-    <row r="76" spans="1:61">
-      <c r="A76" s="62"/>
+      <c r="AS75" s="8"/>
+      <c r="AT75" s="7"/>
+      <c r="AU75" s="5"/>
+      <c r="AV75" s="5"/>
+      <c r="AW75" s="8"/>
+      <c r="BE75" s="5"/>
+      <c r="BF75" s="26"/>
+      <c r="BG75" s="26"/>
+    </row>
+    <row r="76" spans="1:59">
+      <c r="A76" s="36"/>
       <c r="B76" s="8"/>
       <c r="C76" s="7"/>
       <c r="D76" s="5"/>
@@ -5807,7 +5693,7 @@
       <c r="V76" s="8"/>
       <c r="X76" s="16"/>
       <c r="Y76" s="7"/>
-      <c r="Z76" s="60" t="s">
+      <c r="Z76" s="31" t="s">
         <v>39</v>
       </c>
       <c r="AA76" s="5"/>
@@ -5828,19 +5714,17 @@
       <c r="AP76" s="5"/>
       <c r="AQ76" s="8"/>
       <c r="AR76" s="7"/>
-      <c r="AS76" s="5"/>
-      <c r="AT76" s="5"/>
-      <c r="AU76" s="8"/>
-      <c r="AV76" s="7"/>
-      <c r="AW76" s="5"/>
-      <c r="AX76" s="5"/>
-      <c r="AY76" s="8"/>
-      <c r="BG76" s="5"/>
-      <c r="BH76" s="26"/>
-      <c r="BI76" s="26"/>
-    </row>
-    <row r="77" spans="1:61">
-      <c r="A77" s="62"/>
+      <c r="AS76" s="8"/>
+      <c r="AT76" s="7"/>
+      <c r="AU76" s="5"/>
+      <c r="AV76" s="5"/>
+      <c r="AW76" s="8"/>
+      <c r="BE76" s="5"/>
+      <c r="BF76" s="26"/>
+      <c r="BG76" s="26"/>
+    </row>
+    <row r="77" spans="1:59">
+      <c r="A77" s="36"/>
       <c r="B77" s="8"/>
       <c r="C77" s="7"/>
       <c r="D77" s="5"/>
@@ -5864,7 +5748,7 @@
       <c r="V77" s="8"/>
       <c r="X77" s="16"/>
       <c r="Y77" s="7"/>
-      <c r="Z77" s="60" t="s">
+      <c r="Z77" s="31" t="s">
         <v>25</v>
       </c>
       <c r="AA77" s="5"/>
@@ -5885,19 +5769,17 @@
       <c r="AP77" s="5"/>
       <c r="AQ77" s="8"/>
       <c r="AR77" s="7"/>
-      <c r="AS77" s="5"/>
-      <c r="AT77" s="5"/>
-      <c r="AU77" s="8"/>
-      <c r="AV77" s="7"/>
-      <c r="AW77" s="5"/>
-      <c r="AX77" s="5"/>
-      <c r="AY77" s="8"/>
-      <c r="BG77" s="5"/>
-      <c r="BH77" s="26"/>
-      <c r="BI77" s="26"/>
-    </row>
-    <row r="78" spans="1:61">
-      <c r="A78" s="62"/>
+      <c r="AS77" s="8"/>
+      <c r="AT77" s="7"/>
+      <c r="AU77" s="5"/>
+      <c r="AV77" s="5"/>
+      <c r="AW77" s="8"/>
+      <c r="BE77" s="5"/>
+      <c r="BF77" s="26"/>
+      <c r="BG77" s="26"/>
+    </row>
+    <row r="78" spans="1:59">
+      <c r="A78" s="36"/>
       <c r="B78" s="8"/>
       <c r="C78" s="7"/>
       <c r="D78" s="5"/>
@@ -5921,7 +5803,7 @@
       <c r="V78" s="8"/>
       <c r="X78" s="16"/>
       <c r="Y78" s="7"/>
-      <c r="Z78" s="60" t="s">
+      <c r="Z78" s="31" t="s">
         <v>26</v>
       </c>
       <c r="AA78" s="5"/>
@@ -5942,19 +5824,17 @@
       <c r="AP78" s="5"/>
       <c r="AQ78" s="8"/>
       <c r="AR78" s="7"/>
-      <c r="AS78" s="5"/>
-      <c r="AT78" s="5"/>
-      <c r="AU78" s="8"/>
-      <c r="AV78" s="7"/>
-      <c r="AW78" s="5"/>
-      <c r="AX78" s="5"/>
-      <c r="AY78" s="8"/>
-      <c r="BG78" s="5"/>
-      <c r="BH78" s="26"/>
-      <c r="BI78" s="26"/>
-    </row>
-    <row r="79" spans="1:61">
-      <c r="A79" s="62"/>
+      <c r="AS78" s="8"/>
+      <c r="AT78" s="7"/>
+      <c r="AU78" s="5"/>
+      <c r="AV78" s="5"/>
+      <c r="AW78" s="8"/>
+      <c r="BE78" s="5"/>
+      <c r="BF78" s="26"/>
+      <c r="BG78" s="26"/>
+    </row>
+    <row r="79" spans="1:59">
+      <c r="A79" s="36"/>
       <c r="B79" s="8"/>
       <c r="C79" s="7"/>
       <c r="D79" s="5"/>
@@ -5997,19 +5877,17 @@
       <c r="AP79" s="5"/>
       <c r="AQ79" s="8"/>
       <c r="AR79" s="7"/>
-      <c r="AS79" s="5"/>
-      <c r="AT79" s="5"/>
-      <c r="AU79" s="8"/>
-      <c r="AV79" s="7"/>
-      <c r="AW79" s="5"/>
-      <c r="AX79" s="5"/>
-      <c r="AY79" s="8"/>
-      <c r="BG79" s="5"/>
-      <c r="BH79" s="26"/>
-      <c r="BI79" s="26"/>
-    </row>
-    <row r="80" spans="1:61">
-      <c r="A80" s="62"/>
+      <c r="AS79" s="8"/>
+      <c r="AT79" s="7"/>
+      <c r="AU79" s="5"/>
+      <c r="AV79" s="5"/>
+      <c r="AW79" s="8"/>
+      <c r="BE79" s="5"/>
+      <c r="BF79" s="26"/>
+      <c r="BG79" s="26"/>
+    </row>
+    <row r="80" spans="1:59">
+      <c r="A80" s="36"/>
       <c r="B80" s="8"/>
       <c r="C80" s="7"/>
       <c r="D80" s="5"/>
@@ -6054,19 +5932,17 @@
       <c r="AP80" s="5"/>
       <c r="AQ80" s="8"/>
       <c r="AR80" s="7"/>
-      <c r="AS80" s="5"/>
-      <c r="AT80" s="5"/>
-      <c r="AU80" s="8"/>
-      <c r="AV80" s="7"/>
-      <c r="AW80" s="5"/>
-      <c r="AX80" s="5"/>
-      <c r="AY80" s="8"/>
-      <c r="BG80" s="5"/>
-      <c r="BH80" s="26"/>
-      <c r="BI80" s="26"/>
-    </row>
-    <row r="81" spans="1:64">
-      <c r="A81" s="62"/>
+      <c r="AS80" s="8"/>
+      <c r="AT80" s="7"/>
+      <c r="AU80" s="5"/>
+      <c r="AV80" s="5"/>
+      <c r="AW80" s="8"/>
+      <c r="BE80" s="5"/>
+      <c r="BF80" s="26"/>
+      <c r="BG80" s="26"/>
+    </row>
+    <row r="81" spans="1:62">
+      <c r="A81" s="36"/>
       <c r="B81" s="8"/>
       <c r="C81" s="7"/>
       <c r="D81" s="5"/>
@@ -6109,19 +5985,17 @@
       <c r="AP81" s="5"/>
       <c r="AQ81" s="8"/>
       <c r="AR81" s="7"/>
-      <c r="AS81" s="5"/>
-      <c r="AT81" s="5"/>
-      <c r="AU81" s="8"/>
-      <c r="AV81" s="7"/>
-      <c r="AW81" s="5"/>
-      <c r="AX81" s="5"/>
-      <c r="AY81" s="8"/>
-      <c r="BG81" s="5"/>
-      <c r="BH81" s="26"/>
-      <c r="BI81" s="26"/>
-    </row>
-    <row r="82" spans="1:64">
-      <c r="A82" s="62"/>
+      <c r="AS81" s="8"/>
+      <c r="AT81" s="7"/>
+      <c r="AU81" s="5"/>
+      <c r="AV81" s="5"/>
+      <c r="AW81" s="8"/>
+      <c r="BE81" s="5"/>
+      <c r="BF81" s="26"/>
+      <c r="BG81" s="26"/>
+    </row>
+    <row r="82" spans="1:62">
+      <c r="A82" s="36"/>
       <c r="B82" s="8"/>
       <c r="C82" s="7"/>
       <c r="D82" s="5"/>
@@ -6166,19 +6040,17 @@
       <c r="AP82" s="5"/>
       <c r="AQ82" s="8"/>
       <c r="AR82" s="7"/>
-      <c r="AS82" s="5"/>
-      <c r="AT82" s="5"/>
-      <c r="AU82" s="8"/>
-      <c r="AV82" s="7"/>
-      <c r="AW82" s="5"/>
-      <c r="AX82" s="5"/>
-      <c r="AY82" s="8"/>
-      <c r="BG82" s="5"/>
-      <c r="BH82" s="26"/>
-      <c r="BI82" s="26"/>
-    </row>
-    <row r="83" spans="1:64">
-      <c r="A83" s="62"/>
+      <c r="AS82" s="8"/>
+      <c r="AT82" s="7"/>
+      <c r="AU82" s="5"/>
+      <c r="AV82" s="5"/>
+      <c r="AW82" s="8"/>
+      <c r="BE82" s="5"/>
+      <c r="BF82" s="26"/>
+      <c r="BG82" s="26"/>
+    </row>
+    <row r="83" spans="1:62">
+      <c r="A83" s="36"/>
       <c r="B83" s="8"/>
       <c r="C83" s="7"/>
       <c r="D83" s="5"/>
@@ -6223,22 +6095,20 @@
       <c r="AP83" s="5"/>
       <c r="AQ83" s="8"/>
       <c r="AR83" s="7"/>
-      <c r="AS83" s="5"/>
-      <c r="AT83" s="5"/>
-      <c r="AU83" s="8"/>
-      <c r="AV83" s="7"/>
-      <c r="AW83" s="5"/>
-      <c r="AX83" s="5"/>
-      <c r="AY83" s="8"/>
-      <c r="BG83" s="5"/>
-      <c r="BH83" s="26"/>
-      <c r="BI83" s="26"/>
+      <c r="AS83" s="8"/>
+      <c r="AT83" s="7"/>
+      <c r="AU83" s="5"/>
+      <c r="AV83" s="5"/>
+      <c r="AW83" s="8"/>
+      <c r="BE83" s="5"/>
+      <c r="BF83" s="26"/>
+      <c r="BG83" s="26"/>
+      <c r="BH83" s="5"/>
+      <c r="BI83" s="5"/>
       <c r="BJ83" s="5"/>
-      <c r="BK83" s="5"/>
-      <c r="BL83" s="5"/>
-    </row>
-    <row r="84" spans="1:64">
-      <c r="A84" s="62"/>
+    </row>
+    <row r="84" spans="1:62">
+      <c r="A84" s="36"/>
       <c r="B84" s="8"/>
       <c r="C84" s="7"/>
       <c r="D84" s="5"/>
@@ -6283,22 +6153,20 @@
       <c r="AP84" s="5"/>
       <c r="AQ84" s="8"/>
       <c r="AR84" s="7"/>
-      <c r="AS84" s="5"/>
-      <c r="AT84" s="5"/>
-      <c r="AU84" s="8"/>
-      <c r="AV84" s="7"/>
-      <c r="AW84" s="5"/>
-      <c r="AX84" s="5"/>
-      <c r="AY84" s="8"/>
-      <c r="BG84" s="5"/>
-      <c r="BH84" s="26"/>
-      <c r="BI84" s="26"/>
+      <c r="AS84" s="8"/>
+      <c r="AT84" s="7"/>
+      <c r="AU84" s="5"/>
+      <c r="AV84" s="5"/>
+      <c r="AW84" s="8"/>
+      <c r="BE84" s="5"/>
+      <c r="BF84" s="26"/>
+      <c r="BG84" s="26"/>
+      <c r="BH84" s="5"/>
+      <c r="BI84" s="5"/>
       <c r="BJ84" s="5"/>
-      <c r="BK84" s="5"/>
-      <c r="BL84" s="5"/>
-    </row>
-    <row r="85" spans="1:64">
-      <c r="A85" s="62"/>
+    </row>
+    <row r="85" spans="1:62">
+      <c r="A85" s="36"/>
       <c r="B85" s="8"/>
       <c r="C85" s="7"/>
       <c r="D85" s="5"/>
@@ -6343,22 +6211,20 @@
       <c r="AP85" s="5"/>
       <c r="AQ85" s="8"/>
       <c r="AR85" s="7"/>
-      <c r="AS85" s="5"/>
-      <c r="AT85" s="5"/>
-      <c r="AU85" s="8"/>
-      <c r="AV85" s="7"/>
-      <c r="AW85" s="5"/>
-      <c r="AX85" s="5"/>
-      <c r="AY85" s="8"/>
-      <c r="BG85" s="5"/>
-      <c r="BH85" s="26"/>
-      <c r="BI85" s="26"/>
+      <c r="AS85" s="8"/>
+      <c r="AT85" s="7"/>
+      <c r="AU85" s="5"/>
+      <c r="AV85" s="5"/>
+      <c r="AW85" s="8"/>
+      <c r="BE85" s="5"/>
+      <c r="BF85" s="26"/>
+      <c r="BG85" s="26"/>
+      <c r="BH85" s="5"/>
+      <c r="BI85" s="5"/>
       <c r="BJ85" s="5"/>
-      <c r="BK85" s="5"/>
-      <c r="BL85" s="5"/>
-    </row>
-    <row r="86" spans="1:64">
-      <c r="A86" s="62"/>
+    </row>
+    <row r="86" spans="1:62">
+      <c r="A86" s="36"/>
       <c r="B86" s="8"/>
       <c r="C86" s="7"/>
       <c r="D86" s="5"/>
@@ -6403,22 +6269,20 @@
       <c r="AP86" s="5"/>
       <c r="AQ86" s="8"/>
       <c r="AR86" s="7"/>
-      <c r="AS86" s="5"/>
-      <c r="AT86" s="5"/>
-      <c r="AU86" s="8"/>
-      <c r="AV86" s="7"/>
-      <c r="AW86" s="5"/>
-      <c r="AX86" s="5"/>
-      <c r="AY86" s="8"/>
-      <c r="BG86" s="5"/>
-      <c r="BH86" s="26"/>
-      <c r="BI86" s="26"/>
+      <c r="AS86" s="8"/>
+      <c r="AT86" s="7"/>
+      <c r="AU86" s="5"/>
+      <c r="AV86" s="5"/>
+      <c r="AW86" s="8"/>
+      <c r="BE86" s="5"/>
+      <c r="BF86" s="26"/>
+      <c r="BG86" s="26"/>
+      <c r="BH86" s="5"/>
+      <c r="BI86" s="5"/>
       <c r="BJ86" s="5"/>
-      <c r="BK86" s="5"/>
-      <c r="BL86" s="5"/>
-    </row>
-    <row r="87" spans="1:64">
-      <c r="A87" s="62"/>
+    </row>
+    <row r="87" spans="1:62">
+      <c r="A87" s="36"/>
       <c r="B87" s="8"/>
       <c r="C87" s="7"/>
       <c r="D87" s="5"/>
@@ -6463,22 +6327,20 @@
       <c r="AP87" s="5"/>
       <c r="AQ87" s="8"/>
       <c r="AR87" s="7"/>
-      <c r="AS87" s="5"/>
-      <c r="AT87" s="5"/>
-      <c r="AU87" s="8"/>
-      <c r="AV87" s="7"/>
-      <c r="AW87" s="5"/>
-      <c r="AX87" s="5"/>
-      <c r="AY87" s="8"/>
-      <c r="BG87" s="5"/>
-      <c r="BH87" s="26"/>
-      <c r="BI87" s="26"/>
+      <c r="AS87" s="8"/>
+      <c r="AT87" s="7"/>
+      <c r="AU87" s="5"/>
+      <c r="AV87" s="5"/>
+      <c r="AW87" s="8"/>
+      <c r="BE87" s="5"/>
+      <c r="BF87" s="26"/>
+      <c r="BG87" s="26"/>
+      <c r="BH87" s="5"/>
+      <c r="BI87" s="5"/>
       <c r="BJ87" s="5"/>
-      <c r="BK87" s="5"/>
-      <c r="BL87" s="5"/>
-    </row>
-    <row r="88" spans="1:64">
-      <c r="A88" s="62"/>
+    </row>
+    <row r="88" spans="1:62">
+      <c r="A88" s="36"/>
       <c r="B88" s="8"/>
       <c r="C88" s="7"/>
       <c r="D88" s="5"/>
@@ -6522,22 +6384,20 @@
       <c r="AP88" s="5"/>
       <c r="AQ88" s="8"/>
       <c r="AR88" s="7"/>
-      <c r="AS88" s="5"/>
-      <c r="AT88" s="5"/>
-      <c r="AU88" s="8"/>
-      <c r="AV88" s="7"/>
-      <c r="AW88" s="5"/>
-      <c r="AX88" s="5"/>
-      <c r="AY88" s="8"/>
-      <c r="BG88" s="5"/>
-      <c r="BH88" s="26"/>
-      <c r="BI88" s="26"/>
+      <c r="AS88" s="8"/>
+      <c r="AT88" s="7"/>
+      <c r="AU88" s="5"/>
+      <c r="AV88" s="5"/>
+      <c r="AW88" s="8"/>
+      <c r="BE88" s="5"/>
+      <c r="BF88" s="26"/>
+      <c r="BG88" s="26"/>
+      <c r="BH88" s="5"/>
+      <c r="BI88" s="5"/>
       <c r="BJ88" s="5"/>
-      <c r="BK88" s="5"/>
-      <c r="BL88" s="5"/>
-    </row>
-    <row r="89" spans="1:64">
-      <c r="A89" s="62"/>
+    </row>
+    <row r="89" spans="1:62">
+      <c r="A89" s="36"/>
       <c r="B89" s="8"/>
       <c r="C89" s="7"/>
       <c r="D89" s="5"/>
@@ -6581,22 +6441,20 @@
       <c r="AP89" s="5"/>
       <c r="AQ89" s="8"/>
       <c r="AR89" s="7"/>
-      <c r="AS89" s="5"/>
-      <c r="AT89" s="5"/>
-      <c r="AU89" s="8"/>
-      <c r="AV89" s="7"/>
-      <c r="AW89" s="5"/>
-      <c r="AX89" s="5"/>
-      <c r="AY89" s="8"/>
-      <c r="BG89" s="5"/>
-      <c r="BH89" s="26"/>
-      <c r="BI89" s="26"/>
+      <c r="AS89" s="8"/>
+      <c r="AT89" s="7"/>
+      <c r="AU89" s="5"/>
+      <c r="AV89" s="5"/>
+      <c r="AW89" s="8"/>
+      <c r="BE89" s="5"/>
+      <c r="BF89" s="26"/>
+      <c r="BG89" s="26"/>
+      <c r="BH89" s="5"/>
+      <c r="BI89" s="5"/>
       <c r="BJ89" s="5"/>
-      <c r="BK89" s="5"/>
-      <c r="BL89" s="5"/>
-    </row>
-    <row r="90" spans="1:64">
-      <c r="A90" s="62"/>
+    </row>
+    <row r="90" spans="1:62">
+      <c r="A90" s="36"/>
       <c r="B90" s="8"/>
       <c r="C90" s="7"/>
       <c r="D90" s="5"/>
@@ -6640,22 +6498,20 @@
       <c r="AP90" s="5"/>
       <c r="AQ90" s="8"/>
       <c r="AR90" s="7"/>
-      <c r="AS90" s="5"/>
-      <c r="AT90" s="5"/>
-      <c r="AU90" s="8"/>
-      <c r="AV90" s="7"/>
-      <c r="AW90" s="5"/>
-      <c r="AX90" s="5"/>
-      <c r="AY90" s="8"/>
-      <c r="BG90" s="5"/>
-      <c r="BH90" s="26"/>
-      <c r="BI90" s="26"/>
+      <c r="AS90" s="8"/>
+      <c r="AT90" s="7"/>
+      <c r="AU90" s="5"/>
+      <c r="AV90" s="5"/>
+      <c r="AW90" s="8"/>
+      <c r="BE90" s="5"/>
+      <c r="BF90" s="26"/>
+      <c r="BG90" s="26"/>
+      <c r="BH90" s="5"/>
+      <c r="BI90" s="5"/>
       <c r="BJ90" s="5"/>
-      <c r="BK90" s="5"/>
-      <c r="BL90" s="5"/>
-    </row>
-    <row r="91" spans="1:64">
-      <c r="A91" s="62"/>
+    </row>
+    <row r="91" spans="1:62">
+      <c r="A91" s="36"/>
       <c r="B91" s="8"/>
       <c r="C91" s="7"/>
       <c r="D91" s="5"/>
@@ -6700,22 +6556,20 @@
       <c r="AP91" s="5"/>
       <c r="AQ91" s="8"/>
       <c r="AR91" s="7"/>
-      <c r="AS91" s="5"/>
-      <c r="AT91" s="5"/>
-      <c r="AU91" s="8"/>
-      <c r="AV91" s="7"/>
-      <c r="AW91" s="5"/>
-      <c r="AX91" s="5"/>
-      <c r="AY91" s="8"/>
-      <c r="BG91" s="5"/>
-      <c r="BH91" s="26"/>
-      <c r="BI91" s="26"/>
+      <c r="AS91" s="8"/>
+      <c r="AT91" s="7"/>
+      <c r="AU91" s="5"/>
+      <c r="AV91" s="5"/>
+      <c r="AW91" s="8"/>
+      <c r="BE91" s="5"/>
+      <c r="BF91" s="26"/>
+      <c r="BG91" s="26"/>
+      <c r="BH91" s="5"/>
+      <c r="BI91" s="5"/>
       <c r="BJ91" s="5"/>
-      <c r="BK91" s="5"/>
-      <c r="BL91" s="5"/>
-    </row>
-    <row r="92" spans="1:64">
-      <c r="A92" s="63"/>
+    </row>
+    <row r="92" spans="1:62">
+      <c r="A92" s="37"/>
       <c r="B92" s="8"/>
       <c r="C92" s="7"/>
       <c r="D92" s="5"/>
@@ -6760,22 +6614,20 @@
       <c r="AP92" s="5"/>
       <c r="AQ92" s="8"/>
       <c r="AR92" s="7"/>
-      <c r="AS92" s="5"/>
-      <c r="AT92" s="5"/>
-      <c r="AU92" s="8"/>
-      <c r="AV92" s="7"/>
-      <c r="AW92" s="5"/>
-      <c r="AX92" s="5"/>
-      <c r="AY92" s="8"/>
-      <c r="BG92" s="5"/>
-      <c r="BH92" s="26"/>
-      <c r="BI92" s="26"/>
+      <c r="AS92" s="8"/>
+      <c r="AT92" s="7"/>
+      <c r="AU92" s="5"/>
+      <c r="AV92" s="5"/>
+      <c r="AW92" s="8"/>
+      <c r="BE92" s="5"/>
+      <c r="BF92" s="26"/>
+      <c r="BG92" s="26"/>
+      <c r="BH92" s="5"/>
+      <c r="BI92" s="5"/>
       <c r="BJ92" s="5"/>
-      <c r="BK92" s="5"/>
-      <c r="BL92" s="5"/>
-    </row>
-    <row r="93" spans="1:64">
-      <c r="A93" s="67" t="s">
+    </row>
+    <row r="93" spans="1:62" ht="18">
+      <c r="A93" s="38" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="23"/>
@@ -6820,23 +6672,25 @@
       <c r="AO93" s="4"/>
       <c r="AP93" s="4"/>
       <c r="AQ93" s="23"/>
-      <c r="AR93" s="24"/>
-      <c r="AS93" s="4"/>
-      <c r="AT93" s="4"/>
-      <c r="AU93" s="23"/>
-      <c r="AV93" s="24"/>
-      <c r="AW93" s="4"/>
-      <c r="AX93" s="4"/>
-      <c r="AY93" s="23"/>
+      <c r="AR93" s="71">
+        <v>45594</v>
+      </c>
+      <c r="AS93" s="23"/>
+      <c r="AT93" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU93" s="4"/>
+      <c r="AV93" s="4"/>
+      <c r="AW93" s="23"/>
+      <c r="BE93" s="5"/>
+      <c r="BF93" s="5"/>
       <c r="BG93" s="5"/>
       <c r="BH93" s="5"/>
       <c r="BI93" s="5"/>
       <c r="BJ93" s="5"/>
-      <c r="BK93" s="5"/>
-      <c r="BL93" s="5"/>
-    </row>
-    <row r="94" spans="1:64">
-      <c r="A94" s="68"/>
+    </row>
+    <row r="94" spans="1:62">
+      <c r="A94" s="39"/>
       <c r="B94" s="8"/>
       <c r="C94" s="13" t="s">
         <v>29</v>
@@ -6883,16 +6737,14 @@
       <c r="AP94" s="5"/>
       <c r="AQ94" s="8"/>
       <c r="AR94" s="7"/>
-      <c r="AS94" s="5"/>
-      <c r="AT94" s="5"/>
-      <c r="AU94" s="8"/>
-      <c r="AV94" s="7"/>
-      <c r="AW94" s="5"/>
-      <c r="AX94" s="5"/>
-      <c r="AY94" s="8"/>
-    </row>
-    <row r="95" spans="1:64">
-      <c r="A95" s="68"/>
+      <c r="AS94" s="8"/>
+      <c r="AT94" s="7"/>
+      <c r="AU94" s="5"/>
+      <c r="AV94" s="5"/>
+      <c r="AW94" s="8"/>
+    </row>
+    <row r="95" spans="1:62">
+      <c r="A95" s="39"/>
       <c r="B95" s="8">
         <v>1</v>
       </c>
@@ -6941,16 +6793,14 @@
       <c r="AP95" s="5"/>
       <c r="AQ95" s="8"/>
       <c r="AR95" s="7"/>
-      <c r="AS95" s="5"/>
-      <c r="AT95" s="5"/>
-      <c r="AU95" s="8"/>
-      <c r="AV95" s="7"/>
-      <c r="AW95" s="5"/>
-      <c r="AX95" s="5"/>
-      <c r="AY95" s="8"/>
-    </row>
-    <row r="96" spans="1:64">
-      <c r="A96" s="68"/>
+      <c r="AS95" s="8"/>
+      <c r="AT95" s="7"/>
+      <c r="AU95" s="5"/>
+      <c r="AV95" s="5"/>
+      <c r="AW95" s="8"/>
+    </row>
+    <row r="96" spans="1:62">
+      <c r="A96" s="39"/>
       <c r="B96" s="8">
         <v>2</v>
       </c>
@@ -6997,16 +6847,14 @@
       <c r="AP96" s="5"/>
       <c r="AQ96" s="8"/>
       <c r="AR96" s="7"/>
-      <c r="AS96" s="5"/>
-      <c r="AT96" s="5"/>
-      <c r="AU96" s="8"/>
-      <c r="AV96" s="7"/>
-      <c r="AW96" s="5"/>
-      <c r="AX96" s="5"/>
-      <c r="AY96" s="8"/>
-    </row>
-    <row r="97" spans="1:58">
-      <c r="A97" s="68"/>
+      <c r="AS96" s="8"/>
+      <c r="AT96" s="7"/>
+      <c r="AU96" s="5"/>
+      <c r="AV96" s="5"/>
+      <c r="AW96" s="8"/>
+    </row>
+    <row r="97" spans="1:56">
+      <c r="A97" s="39"/>
       <c r="B97" s="8"/>
       <c r="C97" s="7"/>
       <c r="D97" s="5"/>
@@ -7051,16 +6899,14 @@
       <c r="AP97" s="5"/>
       <c r="AQ97" s="8"/>
       <c r="AR97" s="7"/>
-      <c r="AS97" s="5"/>
-      <c r="AT97" s="5"/>
-      <c r="AU97" s="8"/>
-      <c r="AV97" s="7"/>
-      <c r="AW97" s="5"/>
-      <c r="AX97" s="5"/>
-      <c r="AY97" s="8"/>
-    </row>
-    <row r="98" spans="1:58">
-      <c r="A98" s="68"/>
+      <c r="AS97" s="8"/>
+      <c r="AT97" s="7"/>
+      <c r="AU97" s="5"/>
+      <c r="AV97" s="5"/>
+      <c r="AW97" s="8"/>
+    </row>
+    <row r="98" spans="1:56">
+      <c r="A98" s="39"/>
       <c r="B98" s="8"/>
       <c r="C98" s="7"/>
       <c r="D98" s="14" t="s">
@@ -7107,16 +6953,14 @@
       <c r="AP98" s="5"/>
       <c r="AQ98" s="8"/>
       <c r="AR98" s="7"/>
-      <c r="AS98" s="5"/>
-      <c r="AT98" s="5"/>
-      <c r="AU98" s="8"/>
-      <c r="AV98" s="7"/>
-      <c r="AW98" s="5"/>
-      <c r="AX98" s="5"/>
-      <c r="AY98" s="8"/>
-    </row>
-    <row r="99" spans="1:58">
-      <c r="A99" s="68"/>
+      <c r="AS98" s="8"/>
+      <c r="AT98" s="7"/>
+      <c r="AU98" s="5"/>
+      <c r="AV98" s="5"/>
+      <c r="AW98" s="8"/>
+    </row>
+    <row r="99" spans="1:56">
+      <c r="A99" s="39"/>
       <c r="B99" s="8"/>
       <c r="C99" s="7"/>
       <c r="D99" s="5"/>
@@ -7159,16 +7003,14 @@
       <c r="AP99" s="5"/>
       <c r="AQ99" s="8"/>
       <c r="AR99" s="7"/>
-      <c r="AS99" s="5"/>
-      <c r="AT99" s="5"/>
-      <c r="AU99" s="8"/>
-      <c r="AV99" s="7"/>
-      <c r="AW99" s="5"/>
-      <c r="AX99" s="5"/>
-      <c r="AY99" s="8"/>
-    </row>
-    <row r="100" spans="1:58">
-      <c r="A100" s="68"/>
+      <c r="AS99" s="8"/>
+      <c r="AT99" s="7"/>
+      <c r="AU99" s="5"/>
+      <c r="AV99" s="5"/>
+      <c r="AW99" s="8"/>
+    </row>
+    <row r="100" spans="1:56">
+      <c r="A100" s="39"/>
       <c r="B100" s="8"/>
       <c r="C100" s="7"/>
       <c r="D100" s="5"/>
@@ -7213,16 +7055,14 @@
       <c r="AP100" s="5"/>
       <c r="AQ100" s="8"/>
       <c r="AR100" s="7"/>
-      <c r="AS100" s="5"/>
-      <c r="AT100" s="5"/>
-      <c r="AU100" s="8"/>
-      <c r="AV100" s="7"/>
-      <c r="AW100" s="5"/>
-      <c r="AX100" s="5"/>
-      <c r="AY100" s="8"/>
-    </row>
-    <row r="101" spans="1:58">
-      <c r="A101" s="68"/>
+      <c r="AS100" s="8"/>
+      <c r="AT100" s="7"/>
+      <c r="AU100" s="5"/>
+      <c r="AV100" s="5"/>
+      <c r="AW100" s="8"/>
+    </row>
+    <row r="101" spans="1:56">
+      <c r="A101" s="39"/>
       <c r="B101" s="8"/>
       <c r="C101" s="7"/>
       <c r="D101" s="5"/>
@@ -7267,16 +7107,14 @@
       <c r="AP101" s="5"/>
       <c r="AQ101" s="8"/>
       <c r="AR101" s="7"/>
-      <c r="AS101" s="5"/>
-      <c r="AT101" s="5"/>
-      <c r="AU101" s="8"/>
-      <c r="AV101" s="7"/>
-      <c r="AW101" s="5"/>
-      <c r="AX101" s="5"/>
-      <c r="AY101" s="8"/>
-    </row>
-    <row r="102" spans="1:58">
-      <c r="A102" s="68"/>
+      <c r="AS101" s="8"/>
+      <c r="AT101" s="7"/>
+      <c r="AU101" s="5"/>
+      <c r="AV101" s="5"/>
+      <c r="AW101" s="8"/>
+    </row>
+    <row r="102" spans="1:56">
+      <c r="A102" s="39"/>
       <c r="B102" s="8"/>
       <c r="C102" s="7"/>
       <c r="D102" s="5"/>
@@ -7321,16 +7159,14 @@
       <c r="AP102" s="5"/>
       <c r="AQ102" s="8"/>
       <c r="AR102" s="7"/>
-      <c r="AS102" s="5"/>
-      <c r="AT102" s="5"/>
-      <c r="AU102" s="8"/>
-      <c r="AV102" s="7"/>
-      <c r="AW102" s="5"/>
-      <c r="AX102" s="5"/>
-      <c r="AY102" s="8"/>
-    </row>
-    <row r="103" spans="1:58">
-      <c r="A103" s="68"/>
+      <c r="AS102" s="8"/>
+      <c r="AT102" s="7"/>
+      <c r="AU102" s="5"/>
+      <c r="AV102" s="5"/>
+      <c r="AW102" s="8"/>
+    </row>
+    <row r="103" spans="1:56">
+      <c r="A103" s="39"/>
       <c r="B103" s="8"/>
       <c r="C103" s="7"/>
       <c r="D103" s="5"/>
@@ -7373,16 +7209,14 @@
       <c r="AP103" s="5"/>
       <c r="AQ103" s="8"/>
       <c r="AR103" s="7"/>
-      <c r="AS103" s="5"/>
-      <c r="AT103" s="5"/>
-      <c r="AU103" s="8"/>
-      <c r="AV103" s="7"/>
-      <c r="AW103" s="5"/>
-      <c r="AX103" s="5"/>
-      <c r="AY103" s="8"/>
-    </row>
-    <row r="104" spans="1:58">
-      <c r="A104" s="68"/>
+      <c r="AS103" s="8"/>
+      <c r="AT103" s="7"/>
+      <c r="AU103" s="5"/>
+      <c r="AV103" s="5"/>
+      <c r="AW103" s="8"/>
+    </row>
+    <row r="104" spans="1:56">
+      <c r="A104" s="39"/>
       <c r="B104" s="8"/>
       <c r="C104" s="7"/>
       <c r="D104" s="5"/>
@@ -7427,16 +7261,14 @@
       <c r="AP104" s="5"/>
       <c r="AQ104" s="8"/>
       <c r="AR104" s="7"/>
-      <c r="AS104" s="5"/>
-      <c r="AT104" s="5"/>
-      <c r="AU104" s="8"/>
-      <c r="AV104" s="7"/>
-      <c r="AW104" s="5"/>
-      <c r="AX104" s="5"/>
-      <c r="AY104" s="8"/>
-    </row>
-    <row r="105" spans="1:58">
-      <c r="A105" s="68"/>
+      <c r="AS104" s="8"/>
+      <c r="AT104" s="7"/>
+      <c r="AU104" s="5"/>
+      <c r="AV104" s="5"/>
+      <c r="AW104" s="8"/>
+    </row>
+    <row r="105" spans="1:56">
+      <c r="A105" s="39"/>
       <c r="B105" s="8"/>
       <c r="C105" s="7"/>
       <c r="D105" s="5"/>
@@ -7481,16 +7313,14 @@
       <c r="AP105" s="5"/>
       <c r="AQ105" s="8"/>
       <c r="AR105" s="7"/>
-      <c r="AS105" s="5"/>
-      <c r="AT105" s="5"/>
-      <c r="AU105" s="8"/>
-      <c r="AV105" s="7"/>
-      <c r="AW105" s="5"/>
-      <c r="AX105" s="5"/>
-      <c r="AY105" s="8"/>
-    </row>
-    <row r="106" spans="1:58">
-      <c r="A106" s="68"/>
+      <c r="AS105" s="8"/>
+      <c r="AT105" s="7"/>
+      <c r="AU105" s="5"/>
+      <c r="AV105" s="5"/>
+      <c r="AW105" s="8"/>
+    </row>
+    <row r="106" spans="1:56">
+      <c r="A106" s="39"/>
       <c r="B106" s="8"/>
       <c r="C106" s="7"/>
       <c r="D106" s="5"/>
@@ -7532,16 +7362,14 @@
       <c r="AP106" s="5"/>
       <c r="AQ106" s="8"/>
       <c r="AR106" s="7"/>
-      <c r="AS106" s="5"/>
-      <c r="AT106" s="5"/>
-      <c r="AU106" s="8"/>
-      <c r="AV106" s="7"/>
-      <c r="AW106" s="5"/>
-      <c r="AX106" s="5"/>
-      <c r="AY106" s="8"/>
-    </row>
-    <row r="107" spans="1:58">
-      <c r="A107" s="68"/>
+      <c r="AS106" s="8"/>
+      <c r="AT106" s="7"/>
+      <c r="AU106" s="5"/>
+      <c r="AV106" s="5"/>
+      <c r="AW106" s="8"/>
+    </row>
+    <row r="107" spans="1:56">
+      <c r="A107" s="39"/>
       <c r="B107" s="8"/>
       <c r="C107" s="7"/>
       <c r="D107" s="5"/>
@@ -7586,16 +7414,14 @@
       <c r="AP107" s="5"/>
       <c r="AQ107" s="8"/>
       <c r="AR107" s="7"/>
-      <c r="AS107" s="5"/>
-      <c r="AT107" s="5"/>
-      <c r="AU107" s="8"/>
-      <c r="AV107" s="7"/>
-      <c r="AW107" s="5"/>
-      <c r="AX107" s="5"/>
-      <c r="AY107" s="8"/>
-    </row>
-    <row r="108" spans="1:58">
-      <c r="A108" s="68"/>
+      <c r="AS107" s="8"/>
+      <c r="AT107" s="7"/>
+      <c r="AU107" s="5"/>
+      <c r="AV107" s="5"/>
+      <c r="AW107" s="8"/>
+    </row>
+    <row r="108" spans="1:56">
+      <c r="A108" s="39"/>
       <c r="B108" s="8"/>
       <c r="C108" s="7"/>
       <c r="D108" s="5"/>
@@ -7619,7 +7445,7 @@
       <c r="V108" s="8"/>
       <c r="X108" s="16"/>
       <c r="Y108" s="26"/>
-      <c r="Z108" s="64" t="s">
+      <c r="Z108" s="32" t="s">
         <v>40</v>
       </c>
       <c r="AA108" s="5"/>
@@ -7640,16 +7466,14 @@
       <c r="AP108" s="5"/>
       <c r="AQ108" s="8"/>
       <c r="AR108" s="7"/>
-      <c r="AS108" s="5"/>
-      <c r="AT108" s="5"/>
-      <c r="AU108" s="8"/>
-      <c r="AV108" s="7"/>
-      <c r="AW108" s="5"/>
-      <c r="AX108" s="5"/>
-      <c r="AY108" s="8"/>
-    </row>
-    <row r="109" spans="1:58">
-      <c r="A109" s="68"/>
+      <c r="AS108" s="8"/>
+      <c r="AT108" s="7"/>
+      <c r="AU108" s="5"/>
+      <c r="AV108" s="5"/>
+      <c r="AW108" s="8"/>
+    </row>
+    <row r="109" spans="1:56">
+      <c r="A109" s="39"/>
       <c r="B109" s="8"/>
       <c r="C109" s="7"/>
       <c r="D109" s="5"/>
@@ -7673,7 +7497,7 @@
       <c r="V109" s="8"/>
       <c r="X109" s="16"/>
       <c r="Y109" s="26"/>
-      <c r="Z109" s="64" t="s">
+      <c r="Z109" s="32" t="s">
         <v>41</v>
       </c>
       <c r="AA109" s="5"/>
@@ -7694,20 +7518,18 @@
       <c r="AP109" s="5"/>
       <c r="AQ109" s="8"/>
       <c r="AR109" s="7"/>
-      <c r="AS109" s="5"/>
-      <c r="AT109" s="5"/>
-      <c r="AU109" s="8"/>
-      <c r="AV109" s="7"/>
-      <c r="AW109" s="5"/>
-      <c r="AX109" s="5"/>
-      <c r="AY109" s="8"/>
+      <c r="AS109" s="8"/>
+      <c r="AT109" s="7"/>
+      <c r="AU109" s="5"/>
+      <c r="AV109" s="5"/>
+      <c r="AW109" s="8"/>
+      <c r="BA109" s="5"/>
+      <c r="BB109" s="5"/>
       <c r="BC109" s="5"/>
       <c r="BD109" s="5"/>
-      <c r="BE109" s="5"/>
-      <c r="BF109" s="5"/>
-    </row>
-    <row r="110" spans="1:58">
-      <c r="A110" s="68"/>
+    </row>
+    <row r="110" spans="1:56">
+      <c r="A110" s="39"/>
       <c r="B110" s="8"/>
       <c r="C110" s="7"/>
       <c r="D110" s="5"/>
@@ -7731,7 +7553,7 @@
       <c r="V110" s="8"/>
       <c r="X110" s="16"/>
       <c r="Y110" s="26"/>
-      <c r="Z110" s="64" t="s">
+      <c r="Z110" s="32" t="s">
         <v>42</v>
       </c>
       <c r="AA110" s="5"/>
@@ -7752,19 +7574,17 @@
       <c r="AP110" s="5"/>
       <c r="AQ110" s="8"/>
       <c r="AR110" s="7"/>
-      <c r="AS110" s="5"/>
-      <c r="AT110" s="5"/>
-      <c r="AU110" s="8"/>
-      <c r="AV110" s="7"/>
-      <c r="AW110" s="5"/>
-      <c r="AX110" s="5"/>
-      <c r="AY110" s="8"/>
+      <c r="AS110" s="8"/>
+      <c r="AT110" s="7"/>
+      <c r="AU110" s="5"/>
+      <c r="AV110" s="5"/>
+      <c r="AW110" s="8"/>
+      <c r="BA110" s="5"/>
       <c r="BC110" s="5"/>
-      <c r="BE110" s="5"/>
-      <c r="BF110" s="5"/>
-    </row>
-    <row r="111" spans="1:58">
-      <c r="A111" s="68"/>
+      <c r="BD110" s="5"/>
+    </row>
+    <row r="111" spans="1:56">
+      <c r="A111" s="39"/>
       <c r="B111" s="8"/>
       <c r="C111" s="7"/>
       <c r="D111" s="5"/>
@@ -7788,7 +7608,7 @@
       <c r="V111" s="8"/>
       <c r="X111" s="16"/>
       <c r="Y111" s="26"/>
-      <c r="Z111" s="64" t="s">
+      <c r="Z111" s="32" t="s">
         <v>43</v>
       </c>
       <c r="AA111" s="5"/>
@@ -7809,19 +7629,17 @@
       <c r="AP111" s="5"/>
       <c r="AQ111" s="8"/>
       <c r="AR111" s="7"/>
-      <c r="AS111" s="5"/>
-      <c r="AT111" s="5"/>
-      <c r="AU111" s="8"/>
-      <c r="AV111" s="7"/>
-      <c r="AW111" s="5"/>
-      <c r="AX111" s="5"/>
-      <c r="AY111" s="8"/>
+      <c r="AS111" s="8"/>
+      <c r="AT111" s="7"/>
+      <c r="AU111" s="5"/>
+      <c r="AV111" s="5"/>
+      <c r="AW111" s="8"/>
+      <c r="BA111" s="5"/>
       <c r="BC111" s="5"/>
-      <c r="BE111" s="5"/>
-      <c r="BF111" s="5"/>
-    </row>
-    <row r="112" spans="1:58">
-      <c r="A112" s="68"/>
+      <c r="BD111" s="5"/>
+    </row>
+    <row r="112" spans="1:56">
+      <c r="A112" s="39"/>
       <c r="B112" s="8"/>
       <c r="C112" s="7"/>
       <c r="D112" s="5"/>
@@ -7864,19 +7682,17 @@
       <c r="AP112" s="5"/>
       <c r="AQ112" s="8"/>
       <c r="AR112" s="7"/>
-      <c r="AS112" s="5"/>
-      <c r="AT112" s="5"/>
-      <c r="AU112" s="8"/>
-      <c r="AV112" s="7"/>
-      <c r="AW112" s="5"/>
-      <c r="AX112" s="5"/>
-      <c r="AY112" s="8"/>
+      <c r="AS112" s="8"/>
+      <c r="AT112" s="7"/>
+      <c r="AU112" s="5"/>
+      <c r="AV112" s="5"/>
+      <c r="AW112" s="8"/>
+      <c r="BA112" s="5"/>
       <c r="BC112" s="5"/>
-      <c r="BE112" s="5"/>
-      <c r="BF112" s="5"/>
-    </row>
-    <row r="113" spans="1:58">
-      <c r="A113" s="68"/>
+      <c r="BD112" s="5"/>
+    </row>
+    <row r="113" spans="1:56">
+      <c r="A113" s="39"/>
       <c r="B113" s="8"/>
       <c r="C113" s="7"/>
       <c r="D113" s="5"/>
@@ -7899,7 +7715,7 @@
       <c r="U113" s="5"/>
       <c r="V113" s="8"/>
       <c r="X113" s="16"/>
-      <c r="Y113" s="65" t="s">
+      <c r="Y113" s="33" t="s">
         <v>62</v>
       </c>
       <c r="Z113" s="5"/>
@@ -7921,19 +7737,17 @@
       <c r="AP113" s="5"/>
       <c r="AQ113" s="8"/>
       <c r="AR113" s="7"/>
-      <c r="AS113" s="5"/>
-      <c r="AT113" s="5"/>
-      <c r="AU113" s="8"/>
-      <c r="AV113" s="7"/>
-      <c r="AW113" s="5"/>
-      <c r="AX113" s="5"/>
-      <c r="AY113" s="8"/>
+      <c r="AS113" s="8"/>
+      <c r="AT113" s="7"/>
+      <c r="AU113" s="5"/>
+      <c r="AV113" s="5"/>
+      <c r="AW113" s="8"/>
+      <c r="BA113" s="5"/>
       <c r="BC113" s="5"/>
-      <c r="BE113" s="5"/>
-      <c r="BF113" s="5"/>
-    </row>
-    <row r="114" spans="1:58">
-      <c r="A114" s="68"/>
+      <c r="BD113" s="5"/>
+    </row>
+    <row r="114" spans="1:56">
+      <c r="A114" s="39"/>
       <c r="B114" s="8"/>
       <c r="C114" s="7"/>
       <c r="D114" s="5"/>
@@ -7956,7 +7770,7 @@
       <c r="U114" s="5"/>
       <c r="V114" s="8"/>
       <c r="X114" s="16"/>
-      <c r="Y114" s="65"/>
+      <c r="Y114" s="33"/>
       <c r="Z114" s="5"/>
       <c r="AA114" s="5"/>
       <c r="AB114" s="5"/>
@@ -7976,19 +7790,17 @@
       <c r="AP114" s="5"/>
       <c r="AQ114" s="8"/>
       <c r="AR114" s="7"/>
-      <c r="AS114" s="5"/>
-      <c r="AT114" s="5"/>
-      <c r="AU114" s="8"/>
-      <c r="AV114" s="7"/>
-      <c r="AW114" s="5"/>
-      <c r="AX114" s="5"/>
-      <c r="AY114" s="8"/>
+      <c r="AS114" s="8"/>
+      <c r="AT114" s="7"/>
+      <c r="AU114" s="5"/>
+      <c r="AV114" s="5"/>
+      <c r="AW114" s="8"/>
+      <c r="BA114" s="5"/>
       <c r="BC114" s="5"/>
-      <c r="BE114" s="5"/>
-      <c r="BF114" s="5"/>
-    </row>
-    <row r="115" spans="1:58">
-      <c r="A115" s="68"/>
+      <c r="BD114" s="5"/>
+    </row>
+    <row r="115" spans="1:56">
+      <c r="A115" s="39"/>
       <c r="B115" s="8"/>
       <c r="C115" s="7"/>
       <c r="D115" s="5"/>
@@ -8011,7 +7823,7 @@
       <c r="U115" s="5"/>
       <c r="V115" s="8"/>
       <c r="X115" s="16"/>
-      <c r="Y115" s="65" t="s">
+      <c r="Y115" s="33" t="s">
         <v>64</v>
       </c>
       <c r="Z115" s="5"/>
@@ -8033,20 +7845,18 @@
       <c r="AP115" s="5"/>
       <c r="AQ115" s="8"/>
       <c r="AR115" s="7"/>
-      <c r="AS115" s="5"/>
-      <c r="AT115" s="5"/>
-      <c r="AU115" s="8"/>
-      <c r="AV115" s="7"/>
-      <c r="AW115" s="5"/>
-      <c r="AX115" s="5"/>
-      <c r="AY115" s="8"/>
+      <c r="AS115" s="8"/>
+      <c r="AT115" s="7"/>
+      <c r="AU115" s="5"/>
+      <c r="AV115" s="5"/>
+      <c r="AW115" s="8"/>
+      <c r="BA115" s="5"/>
+      <c r="BB115" s="5"/>
       <c r="BC115" s="5"/>
       <c r="BD115" s="5"/>
-      <c r="BE115" s="5"/>
-      <c r="BF115" s="5"/>
-    </row>
-    <row r="116" spans="1:58">
-      <c r="A116" s="69"/>
+    </row>
+    <row r="116" spans="1:56">
+      <c r="A116" s="40"/>
       <c r="B116" s="8"/>
       <c r="C116" s="7"/>
       <c r="D116" s="5"/>
@@ -8069,7 +7879,7 @@
       <c r="U116" s="5"/>
       <c r="V116" s="8"/>
       <c r="X116" s="16"/>
-      <c r="Y116" s="65" t="s">
+      <c r="Y116" s="33" t="s">
         <v>63</v>
       </c>
       <c r="Z116" s="5"/>
@@ -8091,20 +7901,18 @@
       <c r="AP116" s="5"/>
       <c r="AQ116" s="8"/>
       <c r="AR116" s="7"/>
-      <c r="AS116" s="5"/>
-      <c r="AT116" s="5"/>
-      <c r="AU116" s="8"/>
-      <c r="AV116" s="7"/>
-      <c r="AW116" s="5"/>
-      <c r="AX116" s="5"/>
-      <c r="AY116" s="8"/>
+      <c r="AS116" s="8"/>
+      <c r="AT116" s="7"/>
+      <c r="AU116" s="5"/>
+      <c r="AV116" s="5"/>
+      <c r="AW116" s="8"/>
+      <c r="BA116" s="5"/>
+      <c r="BB116" s="5"/>
       <c r="BC116" s="5"/>
       <c r="BD116" s="5"/>
-      <c r="BE116" s="5"/>
-      <c r="BF116" s="5"/>
-    </row>
-    <row r="117" spans="1:58">
-      <c r="A117" s="58"/>
+    </row>
+    <row r="117" spans="1:56">
+      <c r="A117" s="29"/>
       <c r="B117" s="23"/>
       <c r="C117" s="24"/>
       <c r="D117" s="4"/>
@@ -8128,7 +7936,7 @@
       <c r="V117" s="23"/>
       <c r="W117" s="4"/>
       <c r="X117" s="25"/>
-      <c r="Y117" s="66"/>
+      <c r="Y117" s="34"/>
       <c r="Z117" s="4"/>
       <c r="AA117" s="4"/>
       <c r="AB117" s="4"/>
@@ -8148,15 +7956,13 @@
       <c r="AP117" s="4"/>
       <c r="AQ117" s="23"/>
       <c r="AR117" s="24"/>
-      <c r="AS117" s="4"/>
-      <c r="AT117" s="4"/>
-      <c r="AU117" s="23"/>
-      <c r="AV117" s="24"/>
-      <c r="AW117" s="4"/>
-      <c r="AX117" s="4"/>
-      <c r="AY117" s="23"/>
-    </row>
-    <row r="118" spans="1:58">
+      <c r="AS117" s="23"/>
+      <c r="AT117" s="24"/>
+      <c r="AU117" s="4"/>
+      <c r="AV117" s="4"/>
+      <c r="AW117" s="23"/>
+    </row>
+    <row r="118" spans="1:56">
       <c r="A118" s="1"/>
       <c r="B118" s="8"/>
       <c r="C118" s="7"/>
@@ -8200,15 +8006,13 @@
       <c r="AP118" s="5"/>
       <c r="AQ118" s="8"/>
       <c r="AR118" s="7"/>
-      <c r="AS118" s="5"/>
-      <c r="AT118" s="5"/>
-      <c r="AU118" s="8"/>
-      <c r="AV118" s="7"/>
-      <c r="AW118" s="5"/>
-      <c r="AX118" s="5"/>
-      <c r="AY118" s="8"/>
-    </row>
-    <row r="119" spans="1:58">
+      <c r="AS118" s="8"/>
+      <c r="AT118" s="7"/>
+      <c r="AU118" s="5"/>
+      <c r="AV118" s="5"/>
+      <c r="AW118" s="8"/>
+    </row>
+    <row r="119" spans="1:56">
       <c r="A119" s="1"/>
       <c r="B119" s="8"/>
       <c r="C119" s="7"/>
@@ -8252,15 +8056,13 @@
       <c r="AP119" s="5"/>
       <c r="AQ119" s="8"/>
       <c r="AR119" s="7"/>
-      <c r="AS119" s="5"/>
-      <c r="AT119" s="5"/>
-      <c r="AU119" s="8"/>
-      <c r="AV119" s="7"/>
-      <c r="AW119" s="5"/>
-      <c r="AX119" s="5"/>
-      <c r="AY119" s="8"/>
-    </row>
-    <row r="120" spans="1:58">
+      <c r="AS119" s="8"/>
+      <c r="AT119" s="7"/>
+      <c r="AU119" s="5"/>
+      <c r="AV119" s="5"/>
+      <c r="AW119" s="8"/>
+    </row>
+    <row r="120" spans="1:56">
       <c r="A120" s="1"/>
       <c r="B120" s="8"/>
       <c r="C120" s="7"/>
@@ -8304,15 +8106,13 @@
       <c r="AP120" s="5"/>
       <c r="AQ120" s="8"/>
       <c r="AR120" s="7"/>
-      <c r="AS120" s="5"/>
-      <c r="AT120" s="5"/>
-      <c r="AU120" s="8"/>
-      <c r="AV120" s="7"/>
-      <c r="AW120" s="5"/>
-      <c r="AX120" s="5"/>
-      <c r="AY120" s="8"/>
-    </row>
-    <row r="121" spans="1:58">
+      <c r="AS120" s="8"/>
+      <c r="AT120" s="7"/>
+      <c r="AU120" s="5"/>
+      <c r="AV120" s="5"/>
+      <c r="AW120" s="8"/>
+    </row>
+    <row r="121" spans="1:56">
       <c r="A121" s="1"/>
       <c r="B121" s="8"/>
       <c r="C121" s="7"/>
@@ -8356,15 +8156,13 @@
       <c r="AP121" s="5"/>
       <c r="AQ121" s="8"/>
       <c r="AR121" s="7"/>
-      <c r="AS121" s="5"/>
-      <c r="AT121" s="5"/>
-      <c r="AU121" s="8"/>
-      <c r="AV121" s="7"/>
-      <c r="AW121" s="5"/>
-      <c r="AX121" s="5"/>
-      <c r="AY121" s="8"/>
-    </row>
-    <row r="122" spans="1:58">
+      <c r="AS121" s="8"/>
+      <c r="AT121" s="7"/>
+      <c r="AU121" s="5"/>
+      <c r="AV121" s="5"/>
+      <c r="AW121" s="8"/>
+    </row>
+    <row r="122" spans="1:56">
       <c r="A122" s="1"/>
       <c r="B122" s="8"/>
       <c r="C122" s="7"/>
@@ -8408,15 +8206,13 @@
       <c r="AP122" s="5"/>
       <c r="AQ122" s="8"/>
       <c r="AR122" s="7"/>
-      <c r="AS122" s="5"/>
-      <c r="AT122" s="5"/>
-      <c r="AU122" s="8"/>
-      <c r="AV122" s="7"/>
-      <c r="AW122" s="5"/>
-      <c r="AX122" s="5"/>
-      <c r="AY122" s="8"/>
-    </row>
-    <row r="123" spans="1:58">
+      <c r="AS122" s="8"/>
+      <c r="AT122" s="7"/>
+      <c r="AU122" s="5"/>
+      <c r="AV122" s="5"/>
+      <c r="AW122" s="8"/>
+    </row>
+    <row r="123" spans="1:56">
       <c r="A123" s="1"/>
       <c r="B123" s="8"/>
       <c r="C123" s="7"/>
@@ -8460,15 +8256,13 @@
       <c r="AP123" s="5"/>
       <c r="AQ123" s="8"/>
       <c r="AR123" s="7"/>
-      <c r="AS123" s="5"/>
-      <c r="AT123" s="5"/>
-      <c r="AU123" s="8"/>
-      <c r="AV123" s="7"/>
-      <c r="AW123" s="5"/>
-      <c r="AX123" s="5"/>
-      <c r="AY123" s="8"/>
-    </row>
-    <row r="124" spans="1:58">
+      <c r="AS123" s="8"/>
+      <c r="AT123" s="7"/>
+      <c r="AU123" s="5"/>
+      <c r="AV123" s="5"/>
+      <c r="AW123" s="8"/>
+    </row>
+    <row r="124" spans="1:56">
       <c r="A124" s="1"/>
       <c r="B124" s="8"/>
       <c r="C124" s="7"/>
@@ -8512,15 +8306,13 @@
       <c r="AP124" s="5"/>
       <c r="AQ124" s="8"/>
       <c r="AR124" s="7"/>
-      <c r="AS124" s="5"/>
-      <c r="AT124" s="5"/>
-      <c r="AU124" s="8"/>
-      <c r="AV124" s="7"/>
-      <c r="AW124" s="5"/>
-      <c r="AX124" s="5"/>
-      <c r="AY124" s="8"/>
-    </row>
-    <row r="125" spans="1:58">
+      <c r="AS124" s="8"/>
+      <c r="AT124" s="7"/>
+      <c r="AU124" s="5"/>
+      <c r="AV124" s="5"/>
+      <c r="AW124" s="8"/>
+    </row>
+    <row r="125" spans="1:56">
       <c r="A125" s="1"/>
       <c r="B125" s="8"/>
       <c r="C125" s="7"/>
@@ -8564,15 +8356,13 @@
       <c r="AP125" s="5"/>
       <c r="AQ125" s="8"/>
       <c r="AR125" s="7"/>
-      <c r="AS125" s="5"/>
-      <c r="AT125" s="5"/>
-      <c r="AU125" s="8"/>
-      <c r="AV125" s="7"/>
-      <c r="AW125" s="5"/>
-      <c r="AX125" s="5"/>
-      <c r="AY125" s="8"/>
-    </row>
-    <row r="126" spans="1:58">
+      <c r="AS125" s="8"/>
+      <c r="AT125" s="7"/>
+      <c r="AU125" s="5"/>
+      <c r="AV125" s="5"/>
+      <c r="AW125" s="8"/>
+    </row>
+    <row r="126" spans="1:56">
       <c r="A126" s="1"/>
       <c r="B126" s="8"/>
       <c r="C126" s="7"/>
@@ -8616,15 +8406,13 @@
       <c r="AP126" s="5"/>
       <c r="AQ126" s="8"/>
       <c r="AR126" s="7"/>
-      <c r="AS126" s="5"/>
-      <c r="AT126" s="5"/>
-      <c r="AU126" s="8"/>
-      <c r="AV126" s="7"/>
-      <c r="AW126" s="5"/>
-      <c r="AX126" s="5"/>
-      <c r="AY126" s="8"/>
-    </row>
-    <row r="127" spans="1:58">
+      <c r="AS126" s="8"/>
+      <c r="AT126" s="7"/>
+      <c r="AU126" s="5"/>
+      <c r="AV126" s="5"/>
+      <c r="AW126" s="8"/>
+    </row>
+    <row r="127" spans="1:56">
       <c r="A127" s="1"/>
       <c r="B127" s="8"/>
       <c r="C127" s="7"/>
@@ -8668,15 +8456,13 @@
       <c r="AP127" s="5"/>
       <c r="AQ127" s="8"/>
       <c r="AR127" s="7"/>
-      <c r="AS127" s="5"/>
-      <c r="AT127" s="5"/>
-      <c r="AU127" s="8"/>
-      <c r="AV127" s="7"/>
-      <c r="AW127" s="5"/>
-      <c r="AX127" s="5"/>
-      <c r="AY127" s="8"/>
-    </row>
-    <row r="128" spans="1:58">
+      <c r="AS127" s="8"/>
+      <c r="AT127" s="7"/>
+      <c r="AU127" s="5"/>
+      <c r="AV127" s="5"/>
+      <c r="AW127" s="8"/>
+    </row>
+    <row r="128" spans="1:56">
       <c r="A128" s="1"/>
       <c r="B128" s="8"/>
       <c r="C128" s="7"/>
@@ -8720,15 +8506,13 @@
       <c r="AP128" s="5"/>
       <c r="AQ128" s="8"/>
       <c r="AR128" s="7"/>
-      <c r="AS128" s="5"/>
-      <c r="AT128" s="5"/>
-      <c r="AU128" s="8"/>
-      <c r="AV128" s="7"/>
-      <c r="AW128" s="5"/>
-      <c r="AX128" s="5"/>
-      <c r="AY128" s="8"/>
-    </row>
-    <row r="129" spans="1:51">
+      <c r="AS128" s="8"/>
+      <c r="AT128" s="7"/>
+      <c r="AU128" s="5"/>
+      <c r="AV128" s="5"/>
+      <c r="AW128" s="8"/>
+    </row>
+    <row r="129" spans="1:49">
       <c r="A129" s="1"/>
       <c r="B129" s="8"/>
       <c r="C129" s="7"/>
@@ -8772,35 +8556,33 @@
       <c r="AP129" s="5"/>
       <c r="AQ129" s="8"/>
       <c r="AR129" s="7"/>
-      <c r="AS129" s="5"/>
-      <c r="AT129" s="5"/>
-      <c r="AU129" s="8"/>
-      <c r="AV129" s="7"/>
-      <c r="AW129" s="5"/>
-      <c r="AX129" s="5"/>
-      <c r="AY129" s="8"/>
+      <c r="AS129" s="8"/>
+      <c r="AT129" s="7"/>
+      <c r="AU129" s="5"/>
+      <c r="AV129" s="5"/>
+      <c r="AW129" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AT4:AW4"/>
+    <mergeCell ref="A5:A25"/>
+    <mergeCell ref="A26:A58"/>
+    <mergeCell ref="C4:V4"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="AK1:AR1"/>
+    <mergeCell ref="AU1:AW2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="W2:AF2"/>
+    <mergeCell ref="AG2:AJ2"/>
+    <mergeCell ref="AK2:AR2"/>
+    <mergeCell ref="AS1:AT2"/>
     <mergeCell ref="A60:A92"/>
     <mergeCell ref="A93:A116"/>
     <mergeCell ref="A1:R2"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="W1:AF1"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="AK1:AS1"/>
-    <mergeCell ref="AV1:AX2"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="W2:AF2"/>
-    <mergeCell ref="AG2:AJ2"/>
-    <mergeCell ref="AK2:AS2"/>
-    <mergeCell ref="AT1:AU2"/>
     <mergeCell ref="Y4:AQ4"/>
-    <mergeCell ref="AR4:AU4"/>
-    <mergeCell ref="AV4:AY4"/>
-    <mergeCell ref="A5:A25"/>
-    <mergeCell ref="A26:A58"/>
-    <mergeCell ref="C4:V4"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
